--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,16 +58,277 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
     <t>01921560</t>
   </si>
   <si>
     <t>Trần Quang Hiệu</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
   </si>
   <si>
     <t>09/09/2026 14:00:00</t>
@@ -76,160 +337,136 @@
     <t>09/09/2026 15:30:00</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>Tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
   </si>
   <si>
     <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
   </si>
   <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
   </si>
   <si>
     <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
   </si>
   <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>lắp rack bobin tại xưởng 3</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
   </si>
   <si>
     <t>02022158</t>
@@ -241,19 +478,79 @@
     <t>Hỗ trợ sản xuất(ca 3)</t>
   </si>
   <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
+    <t>tăng ca sản xuất ca2</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>Thay đổi nhân sự</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
   </si>
   <si>
     <t>Hỗ trợ sản xuất(ca 2)</t>
   </si>
   <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
   </si>
   <si>
     <t>02227708</t>
@@ -262,34 +559,76 @@
     <t>Phạm Việt Khải</t>
   </si>
   <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
     <t>Tăng ca hỗ trợ sản xuất (HC)</t>
   </si>
   <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>10/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 15:30:00</t>
   </si>
   <si>
     <t>02020497</t>
@@ -301,19 +640,10 @@
     <t>Tăng ca hổ trợ sản xuất (HC)</t>
   </si>
   <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
   </si>
   <si>
     <t>02021131</t>
@@ -325,18 +655,6 @@
     <t xml:space="preserve">Tăng ca sản xuất </t>
   </si>
   <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
     <t>02021742</t>
   </si>
   <si>
@@ -346,204 +664,33 @@
     <t>tăng ca hỗ trợ sản xuất ca 2</t>
   </si>
   <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
     <t>tăng ca hỗ trợ sản xuất ca 1</t>
   </si>
   <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
-    <t>02224288</t>
-  </si>
-  <si>
-    <t>Võ Văn Dương</t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>Thay đổi nhân sự</t>
-  </si>
-  <si>
-    <t>Từ chối</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>Tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
     <t>02022149</t>
   </si>
   <si>
     <t>Nguyễn Xuân Mạnh</t>
   </si>
   <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 2</t>
-  </si>
-  <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
     <t>02325310</t>
   </si>
   <si>
     <t>Nguyễn Công Hậu</t>
   </si>
   <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
+  </si>
+  <si>
     <t>tăng ca hỗ trợ sản xuất (ca3)</t>
   </si>
   <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
-  </si>
-  <si>
     <t>02325365</t>
   </si>
   <si>
@@ -553,46 +700,31 @@
     <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
   </si>
   <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>02645250</t>
   </si>
   <si>
     <t>Trần Xuân Bắc</t>
   </si>
   <si>
+    <t xml:space="preserve">Tăng ca thứ 7 </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền CA 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
     <t>Hỗ trợ nghiền CA 1</t>
   </si>
   <si>
-    <t>Tăng ca hỗ trợ nghiền CA 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca thứ 7 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+    <t>Tăng ca hỗ trợ nghiền CA 1</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
   </si>
   <si>
     <t>07/09/2026 14:00:00</t>
@@ -604,142 +736,22 @@
     <t>Hỗ trợ nghiền Ca1</t>
   </si>
   <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền CA 1</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>lắp rack bobin tại xưởng 3</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca2</t>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>24/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -1240,10 +1252,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>15</v>
@@ -1252,10 +1264,10 @@
         <v>16</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="8">
         <v>480</v>
@@ -1267,7 +1279,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -1288,10 +1300,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5" s="8">
         <v>480</v>
@@ -1303,7 +1315,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
@@ -1312,10 +1324,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
@@ -1324,13 +1336,13 @@
         <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G6" s="8">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>19</v>
@@ -1339,7 +1351,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -1348,10 +1360,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -1360,10 +1372,10 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G7" s="8">
         <v>480</v>
@@ -1375,7 +1387,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -1384,22 +1396,22 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G8" s="8">
         <v>480</v>
@@ -1411,7 +1423,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1420,10 +1432,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -1432,13 +1444,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G9" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>19</v>
@@ -1447,7 +1459,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1456,23 +1468,23 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="G10" s="8">
         <v>480</v>
       </c>
@@ -1483,7 +1495,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -1492,25 +1504,25 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>19</v>
@@ -1519,7 +1531,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1528,10 +1540,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
@@ -1540,13 +1552,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>19</v>
@@ -1555,7 +1567,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1564,10 +1576,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1576,13 +1588,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G13" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -1591,7 +1603,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1600,10 +1612,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1612,13 +1624,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="G14" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>19</v>
@@ -1636,22 +1648,22 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G15" s="8">
         <v>480</v>
@@ -1663,7 +1675,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1672,10 +1684,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
@@ -1684,7 +1696,7 @@
         <v>16</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>26</v>
@@ -1699,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1708,34 +1720,34 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="8">
+        <v>480</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="8">
-        <v>480</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1744,10 +1756,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1756,13 +1768,13 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="G18" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>19</v>
@@ -1771,7 +1783,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1780,22 +1792,22 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="F19" s="8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G19" s="8">
         <v>480</v>
@@ -1807,7 +1819,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1816,34 +1828,34 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="8">
+        <v>480</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="8">
-        <v>480</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1852,10 +1864,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1864,13 +1876,13 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G21" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>19</v>
@@ -1879,7 +1891,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1888,10 +1900,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1900,10 +1912,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G22" s="8">
         <v>480</v>
@@ -1915,7 +1927,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1924,10 +1936,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1936,10 +1948,10 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G23" s="8">
         <v>480</v>
@@ -1951,7 +1963,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
@@ -1960,10 +1972,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1972,10 +1984,10 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G24" s="8">
         <v>480</v>
@@ -1987,7 +1999,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -1996,10 +2008,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
@@ -2008,13 +2020,13 @@
         <v>16</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="G25" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
@@ -2023,7 +2035,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -2032,10 +2044,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -2044,13 +2056,13 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="G26" s="8">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>19</v>
@@ -2059,7 +2071,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -2068,10 +2080,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -2080,10 +2092,10 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G27" s="8">
         <v>480</v>
@@ -2095,7 +2107,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -2104,10 +2116,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>15</v>
@@ -2116,13 +2128,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="G28" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
@@ -2131,7 +2143,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -2140,10 +2152,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -2152,13 +2164,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="G29" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>19</v>
@@ -2167,7 +2179,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -2176,10 +2188,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -2188,22 +2200,22 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="4">
+        <v>480</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" s="4">
-        <v>120</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -2212,10 +2224,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -2224,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="G31" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>19</v>
@@ -2239,7 +2251,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -2248,10 +2260,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -2260,10 +2272,10 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="G32" s="4">
         <v>480</v>
@@ -2275,7 +2287,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -2284,10 +2296,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -2296,13 +2308,13 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="G33" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>19</v>
@@ -2311,7 +2323,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -2320,10 +2332,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2332,13 +2344,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="G34" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -2347,7 +2359,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -2356,10 +2368,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2368,13 +2380,13 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="G35" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>19</v>
@@ -2383,7 +2395,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2392,10 +2404,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2404,13 +2416,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="G36" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>19</v>
@@ -2419,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2428,10 +2440,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2440,10 +2452,10 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G37" s="4">
         <v>480</v>
@@ -2455,7 +2467,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2464,10 +2476,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2476,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="G38" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2491,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2500,10 +2512,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2512,13 +2524,13 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G39" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>19</v>
@@ -2527,7 +2539,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2536,10 +2548,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2548,10 +2560,10 @@
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G40" s="4">
         <v>480</v>
@@ -2563,7 +2575,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2572,10 +2584,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2584,13 +2596,13 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="G41" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>19</v>
@@ -2599,7 +2611,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2608,10 +2620,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2620,13 +2632,13 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="G42" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>19</v>
@@ -2635,7 +2647,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2644,10 +2656,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2656,22 +2668,22 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="G43" s="4">
+        <v>90</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2680,10 +2692,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
@@ -2692,13 +2704,13 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="G44" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>19</v>
@@ -2707,7 +2719,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2716,10 +2728,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2728,7 +2740,7 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>26</v>
@@ -2743,7 +2755,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2752,10 +2764,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2764,13 +2776,13 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G46" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>19</v>
@@ -2779,7 +2791,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2788,10 +2800,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2800,10 +2812,10 @@
         <v>16</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G47" s="4">
         <v>480</v>
@@ -2815,7 +2827,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2824,10 +2836,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2836,10 +2848,10 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="G48" s="4">
         <v>90</v>
@@ -2851,7 +2863,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2872,10 +2884,10 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G49" s="4">
         <v>480</v>
@@ -2887,7 +2899,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2896,10 +2908,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -2908,10 +2920,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G50" s="4">
         <v>480</v>
@@ -2923,7 +2935,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2932,10 +2944,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
@@ -2944,13 +2956,13 @@
         <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="G51" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>19</v>
@@ -2959,19 +2971,19 @@
         <v>20</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="4" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -2980,10 +2992,10 @@
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="G52" s="4">
         <v>120</v>
@@ -3004,10 +3016,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -3016,10 +3028,10 @@
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="G53" s="4">
         <v>120</v>
@@ -3031,7 +3043,7 @@
         <v>20</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="4" t="s">
@@ -3040,10 +3052,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
@@ -3052,13 +3064,13 @@
         <v>16</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G54" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>19</v>
@@ -3067,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="4" t="s">
@@ -3076,10 +3088,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -3088,13 +3100,13 @@
         <v>16</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="G55" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>19</v>
@@ -3103,7 +3115,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="4" t="s">
@@ -3112,10 +3124,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -3124,13 +3136,13 @@
         <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="G56" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>19</v>
@@ -3139,7 +3151,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
@@ -3148,10 +3160,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -3160,13 +3172,13 @@
         <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="G57" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>19</v>
@@ -3175,7 +3187,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="4" t="s">
@@ -3184,10 +3196,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -3196,13 +3208,13 @@
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>26</v>
+        <v>137</v>
       </c>
       <c r="G58" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>19</v>
@@ -3211,7 +3223,7 @@
         <v>20</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="4" t="s">
@@ -3220,22 +3232,22 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G59" s="4">
         <v>480</v>
@@ -3247,7 +3259,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="4" t="s">
@@ -3256,10 +3268,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -3268,13 +3280,13 @@
         <v>16</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="G60" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>19</v>
@@ -3283,7 +3295,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
@@ -3292,10 +3304,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3304,13 +3316,13 @@
         <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="G61" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>19</v>
@@ -3319,36 +3331,34 @@
         <v>20</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>145</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="K61" s="3"/>
       <c r="L61" s="4" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G62" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>19</v>
@@ -3357,7 +3367,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="4" t="s">
@@ -3378,13 +3388,13 @@
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>137</v>
+        <v>53</v>
       </c>
       <c r="G63" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>19</v>
@@ -3393,7 +3403,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="4" t="s">
@@ -3402,10 +3412,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -3414,13 +3424,13 @@
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="G64" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>19</v>
@@ -3429,7 +3439,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="4" t="s">
@@ -3438,10 +3448,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -3450,10 +3460,10 @@
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="G65" s="4">
         <v>480</v>
@@ -3474,25 +3484,25 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="F66" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G66" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>19</v>
@@ -3501,11 +3511,13 @@
         <v>20</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K66" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="L66" s="4" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67">
@@ -3522,13 +3534,13 @@
         <v>16</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G67" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>19</v>
@@ -3537,7 +3549,7 @@
         <v>20</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="4" t="s">
@@ -3546,10 +3558,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
@@ -3558,13 +3570,13 @@
         <v>16</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G68" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>19</v>
@@ -3573,7 +3585,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="4" t="s">
@@ -3582,10 +3594,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
@@ -3594,13 +3606,13 @@
         <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G69" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>19</v>
@@ -3609,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="s">
@@ -3618,10 +3630,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
@@ -3630,13 +3642,13 @@
         <v>16</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="G70" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>19</v>
@@ -3645,7 +3657,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="s">
@@ -3654,10 +3666,10 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>15</v>
@@ -3666,10 +3678,10 @@
         <v>16</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G71" s="4">
         <v>480</v>
@@ -3681,7 +3693,7 @@
         <v>20</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="4" t="s">
@@ -3690,10 +3702,10 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
@@ -3702,10 +3714,10 @@
         <v>16</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G72" s="4">
         <v>90</v>
@@ -3717,7 +3729,7 @@
         <v>20</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="4" t="s">
@@ -3726,10 +3738,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -3738,10 +3750,10 @@
         <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="G73" s="4">
         <v>480</v>
@@ -3753,7 +3765,7 @@
         <v>20</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>35</v>
+        <v>169</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="s">
@@ -3762,10 +3774,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -3774,10 +3786,10 @@
         <v>16</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G74" s="4">
         <v>90</v>
@@ -3789,7 +3801,7 @@
         <v>20</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="s">
@@ -3798,10 +3810,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>15</v>
@@ -3810,10 +3822,10 @@
         <v>16</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G75" s="4">
         <v>480</v>
@@ -3825,7 +3837,7 @@
         <v>20</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="s">
@@ -3834,10 +3846,10 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
@@ -3846,13 +3858,13 @@
         <v>16</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="G76" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>19</v>
@@ -3861,7 +3873,7 @@
         <v>20</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="s">
@@ -3870,10 +3882,10 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>15</v>
@@ -3882,13 +3894,13 @@
         <v>16</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="G77" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>19</v>
@@ -3897,7 +3909,7 @@
         <v>20</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="s">
@@ -3906,10 +3918,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
@@ -3918,10 +3930,10 @@
         <v>16</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>17</v>
+        <v>167</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="G78" s="4">
         <v>90</v>
@@ -3933,7 +3945,7 @@
         <v>20</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="4" t="s">
@@ -3942,10 +3954,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -3954,13 +3966,13 @@
         <v>16</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G79" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>19</v>
@@ -3969,7 +3981,7 @@
         <v>20</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="s">
@@ -3978,10 +3990,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
@@ -3990,13 +4002,13 @@
         <v>16</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G80" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>19</v>
@@ -4005,7 +4017,7 @@
         <v>20</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="s">
@@ -4014,10 +4026,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>15</v>
@@ -4026,10 +4038,10 @@
         <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="G81" s="4">
         <v>480</v>
@@ -4041,7 +4053,7 @@
         <v>20</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="s">
@@ -4050,10 +4062,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
@@ -4062,13 +4074,13 @@
         <v>16</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>179</v>
+        <v>53</v>
       </c>
       <c r="G82" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>19</v>
@@ -4077,7 +4089,7 @@
         <v>20</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="s">
@@ -4086,10 +4098,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
@@ -4098,13 +4110,13 @@
         <v>16</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>181</v>
+        <v>25</v>
       </c>
       <c r="G83" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>19</v>
@@ -4113,7 +4125,7 @@
         <v>20</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="4" t="s">
@@ -4122,10 +4134,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>15</v>
@@ -4134,13 +4146,13 @@
         <v>16</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>27</v>
+        <v>96</v>
       </c>
       <c r="G84" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>19</v>
@@ -4149,7 +4161,7 @@
         <v>20</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="s">
@@ -4158,10 +4170,10 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
@@ -4170,10 +4182,10 @@
         <v>16</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G85" s="4">
         <v>90</v>
@@ -4185,7 +4197,7 @@
         <v>20</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="K85" s="3"/>
       <c r="L85" s="4" t="s">
@@ -4194,10 +4206,10 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>15</v>
@@ -4206,13 +4218,13 @@
         <v>16</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>184</v>
+        <v>53</v>
       </c>
       <c r="G86" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>19</v>
@@ -4221,7 +4233,7 @@
         <v>20</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="s">
@@ -4230,10 +4242,10 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>15</v>
@@ -4242,10 +4254,10 @@
         <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="G87" s="4">
         <v>90</v>
@@ -4257,7 +4269,7 @@
         <v>20</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="s">
@@ -4266,10 +4278,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -4278,10 +4290,10 @@
         <v>16</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="G88" s="4">
         <v>90</v>
@@ -4293,7 +4305,7 @@
         <v>20</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="s">
@@ -4302,10 +4314,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -4314,10 +4326,10 @@
         <v>16</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="G89" s="4">
         <v>90</v>
@@ -4329,7 +4341,7 @@
         <v>20</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="s">
@@ -4338,10 +4350,10 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
@@ -4350,13 +4362,13 @@
         <v>16</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="G90" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>19</v>
@@ -4365,7 +4377,7 @@
         <v>20</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="s">
@@ -4374,10 +4386,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>15</v>
@@ -4386,10 +4398,10 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G91" s="4">
         <v>90</v>
@@ -4401,7 +4413,7 @@
         <v>20</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="s">
@@ -4410,10 +4422,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>15</v>
@@ -4422,10 +4434,10 @@
         <v>16</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G92" s="4">
         <v>480</v>
@@ -4437,7 +4449,7 @@
         <v>20</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="4" t="s">
@@ -4446,10 +4458,10 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>15</v>
@@ -4458,13 +4470,13 @@
         <v>16</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>192</v>
+        <v>25</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="G93" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>19</v>
@@ -4473,7 +4485,7 @@
         <v>20</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="s">
@@ -4491,16 +4503,16 @@
         <v>15</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="G94" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>19</v>
@@ -4518,10 +4530,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>15</v>
@@ -4530,10 +4542,10 @@
         <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="G95" s="4">
         <v>90</v>
@@ -4545,7 +4557,7 @@
         <v>20</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="s">
@@ -4554,10 +4566,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>187</v>
+        <v>65</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>15</v>
@@ -4566,13 +4578,13 @@
         <v>16</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>201</v>
+        <v>28</v>
       </c>
       <c r="G96" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>19</v>
@@ -4581,7 +4593,7 @@
         <v>20</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>191</v>
+        <v>66</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="s">
@@ -4590,10 +4602,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>15</v>
@@ -4602,10 +4614,10 @@
         <v>16</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="G97" s="4">
         <v>90</v>
@@ -4617,7 +4629,7 @@
         <v>20</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="s">
@@ -4635,16 +4647,16 @@
         <v>15</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>62</v>
+        <v>203</v>
       </c>
       <c r="G98" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>19</v>
@@ -4653,7 +4665,7 @@
         <v>20</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="s">
@@ -4662,10 +4674,10 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>15</v>
@@ -4674,13 +4686,13 @@
         <v>16</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G99" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>19</v>
@@ -4689,7 +4701,7 @@
         <v>20</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="s">
@@ -4698,10 +4710,10 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>15</v>
@@ -4710,13 +4722,13 @@
         <v>16</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>61</v>
+        <v>207</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="G100" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>19</v>
@@ -4725,7 +4737,7 @@
         <v>20</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="s">
@@ -4734,10 +4746,10 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>15</v>
@@ -4746,13 +4758,13 @@
         <v>16</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="G101" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>19</v>
@@ -4761,7 +4773,7 @@
         <v>20</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="s">
@@ -4770,10 +4782,10 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>15</v>
@@ -4782,13 +4794,13 @@
         <v>16</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>211</v>
+        <v>17</v>
       </c>
       <c r="G102" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>19</v>
@@ -4797,7 +4809,7 @@
         <v>20</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="s">
@@ -4806,10 +4818,10 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>15</v>
@@ -4818,10 +4830,10 @@
         <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G103" s="4">
         <v>90</v>
@@ -4833,7 +4845,7 @@
         <v>20</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="s">
@@ -4842,10 +4854,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>15</v>
@@ -4854,22 +4866,22 @@
         <v>16</v>
       </c>
       <c r="E104" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="4">
+        <v>480</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G104" s="4">
-        <v>90</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="s">
@@ -4878,10 +4890,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>15</v>
@@ -4890,13 +4902,13 @@
         <v>16</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="G105" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>19</v>
@@ -4905,7 +4917,7 @@
         <v>20</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="4" t="s">
@@ -4914,10 +4926,10 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>15</v>
@@ -4926,10 +4938,10 @@
         <v>16</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G106" s="4">
         <v>480</v>
@@ -4941,7 +4953,7 @@
         <v>20</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="K106" s="3"/>
       <c r="L106" s="4" t="s">
@@ -4950,10 +4962,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>15</v>
@@ -4962,13 +4974,13 @@
         <v>16</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>221</v>
+        <v>37</v>
       </c>
       <c r="G107" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>19</v>
@@ -4977,7 +4989,7 @@
         <v>20</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="s">
@@ -4986,10 +4998,10 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>15</v>
@@ -4998,13 +5010,13 @@
         <v>16</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="G108" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>19</v>
@@ -5013,7 +5025,7 @@
         <v>20</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="s">
@@ -5022,10 +5034,10 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>15</v>
@@ -5034,10 +5046,10 @@
         <v>16</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G109" s="4">
         <v>480</v>
@@ -5049,7 +5061,7 @@
         <v>20</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="s">
@@ -5058,10 +5070,10 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>15</v>
@@ -5070,13 +5082,13 @@
         <v>16</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="G110" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>19</v>
@@ -5085,7 +5097,7 @@
         <v>20</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="s">
@@ -5094,10 +5106,10 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>15</v>
@@ -5106,10 +5118,10 @@
         <v>16</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="G111" s="4">
         <v>90</v>
@@ -5121,7 +5133,7 @@
         <v>20</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="s">
@@ -5130,10 +5142,10 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>15</v>
@@ -5142,13 +5154,13 @@
         <v>16</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>48</v>
+        <v>199</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="G112" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>19</v>
@@ -5157,7 +5169,7 @@
         <v>20</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="s">
@@ -5166,10 +5178,10 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>15</v>
@@ -5178,10 +5190,10 @@
         <v>16</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G113" s="4">
         <v>480</v>
@@ -5193,7 +5205,7 @@
         <v>20</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="s">
@@ -5202,10 +5214,10 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>15</v>
@@ -5214,13 +5226,13 @@
         <v>16</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>229</v>
+        <v>104</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>230</v>
+        <v>105</v>
       </c>
       <c r="G114" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>19</v>
@@ -5229,7 +5241,7 @@
         <v>20</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="s">
@@ -5238,10 +5250,10 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>15</v>
@@ -5250,13 +5262,13 @@
         <v>16</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="G115" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>19</v>
@@ -5274,25 +5286,25 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E116" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>33</v>
-      </c>
       <c r="G116" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>19</v>
@@ -5301,7 +5313,7 @@
         <v>20</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="s">
@@ -5310,10 +5322,10 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>15</v>
@@ -5322,13 +5334,13 @@
         <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>54</v>
+        <v>236</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="G117" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>19</v>
@@ -5337,7 +5349,7 @@
         <v>20</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="s">
@@ -5346,10 +5358,10 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>15</v>
@@ -5358,13 +5370,13 @@
         <v>16</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="G118" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>19</v>
@@ -5373,7 +5385,7 @@
         <v>20</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="s">
@@ -5382,38 +5394,38 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>31</v>
+        <v>241</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>26</v>
+        <v>242</v>
       </c>
       <c r="G119" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K119" s="3"/>
       <c r="L119" s="4" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,36 +58,51 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>12/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
     <t>02020390</t>
   </si>
   <si>
     <t>Võ Thiên Tuế</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>12/09/2026 22:00:00</t>
   </si>
   <si>
     <t>13/09/2026 06:00:00</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>tăng ca sản xuất</t>
   </si>
   <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
     <t>01921551</t>
   </si>
   <si>
@@ -103,84 +118,603 @@
     <t xml:space="preserve">hỗ trợ sản xuất </t>
   </si>
   <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
     <t>19/09/2026 14:00:00</t>
   </si>
   <si>
     <t>Tăng ca sản xuất</t>
   </si>
   <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>Tăng ca hổ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>Tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>26/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>23/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>23/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
+  </si>
+  <si>
+    <t>Thay đổi nhân sự</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>02645250</t>
+  </si>
+  <si>
+    <t>Trần Xuân Bắc</t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca thứ 7 </t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>lắp rack bobin tại xưởng 3</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>10/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền CA 3</t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>11/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền CA 1</t>
+  </si>
+  <si>
+    <t>Hỗ trợ nghiền CA 1</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>17/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>Hỗ trợ nghiền Ca1</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
     <t>01920589</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Thiện</t>
   </si>
   <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hổ trợ sản xuất </t>
   </si>
   <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t>12/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
   </si>
   <si>
@@ -193,42 +727,6 @@
     <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
   </si>
   <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 06:00:00</t>
-  </si>
-  <si>
     <t>02020965</t>
   </si>
   <si>
@@ -238,177 +736,6 @@
     <t>tăng ca hỗ trợ sản xuất, ca 3</t>
   </si>
   <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>01921560</t>
-  </si>
-  <si>
-    <t>Trần Quang Hiệu</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>Tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>02224288</t>
-  </si>
-  <si>
-    <t>Võ Văn Dương</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
     <t>02222785</t>
   </si>
   <si>
@@ -418,36 +745,6 @@
     <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
   </si>
   <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
     <t>02241656</t>
   </si>
   <si>
@@ -457,301 +754,28 @@
     <t xml:space="preserve">tăng ca sản xuất ca3 </t>
   </si>
   <si>
-    <t>lắp rack bobin tại xưởng 3</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
-  </si>
-  <si>
     <t>tăng ca sản xuất ca2</t>
   </si>
   <si>
-    <t>23/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>23/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca lắp rack bonbin </t>
-  </si>
-  <si>
-    <t>Thay đổi nhân sự</t>
-  </si>
-  <si>
-    <t>Từ chối</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>Tăng ca hổ trợ sản xuất (HC)</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca3)</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
-  </si>
-  <si>
-    <t>02645250</t>
-  </si>
-  <si>
-    <t>Trần Xuân Bắc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca thứ 7 </t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền CA 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
-  </si>
-  <si>
-    <t>Hỗ trợ nghiền CA 1</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền CA 1</t>
-  </si>
-  <si>
-    <t>17/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>Hỗ trợ nghiền Ca1</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>24/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>25/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca đáp ứng tiến độ sản xuất</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tang ca cat ong nhua</t>
   </si>
 </sst>
 </file>
@@ -1288,10 +1312,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>15</v>
@@ -1300,10 +1324,10 @@
         <v>16</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G5" s="8">
         <v>480</v>
@@ -1315,7 +1339,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
@@ -1324,34 +1348,34 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8">
+        <v>480</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="8">
-        <v>180</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>34</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -1360,34 +1384,34 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8">
+        <v>480</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="8">
-        <v>480</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -1396,25 +1420,25 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>19</v>
@@ -1423,7 +1447,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1432,10 +1456,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -1444,10 +1468,10 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G9" s="8">
         <v>480</v>
@@ -1459,7 +1483,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1468,10 +1492,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -1480,13 +1504,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -1495,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -1504,22 +1528,22 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="G11" s="8">
         <v>90</v>
@@ -1531,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1540,22 +1564,22 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="8">
         <v>480</v>
@@ -1567,7 +1591,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1576,10 +1600,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
@@ -1588,13 +1612,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G13" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>19</v>
@@ -1612,10 +1636,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
@@ -1624,10 +1648,10 @@
         <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G14" s="8">
         <v>480</v>
@@ -1639,7 +1663,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
@@ -1648,22 +1672,22 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G15" s="8">
         <v>480</v>
@@ -1675,7 +1699,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1684,34 +1708,34 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="8">
+        <v>480</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="8">
-        <v>480</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1720,34 +1744,34 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="8">
+        <v>480</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="8">
-        <v>480</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1756,10 +1780,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1768,22 +1792,22 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="8">
+        <v>480</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="G18" s="8">
-        <v>90</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
@@ -1792,34 +1816,34 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="8">
+        <v>480</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="8">
-        <v>480</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1828,10 +1852,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1855,7 +1879,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1864,10 +1888,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1876,10 +1900,10 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G21" s="8">
         <v>480</v>
@@ -1891,7 +1915,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1900,34 +1924,34 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="8">
+        <v>480</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="8">
-        <v>480</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1936,10 +1960,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1948,10 +1972,10 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G23" s="8">
         <v>480</v>
@@ -1963,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
@@ -1972,10 +1996,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -1984,10 +2008,10 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G24" s="8">
         <v>480</v>
@@ -1999,7 +2023,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -2008,10 +2032,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
@@ -2020,13 +2044,13 @@
         <v>16</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G25" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
@@ -2035,7 +2059,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -2044,10 +2068,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -2056,10 +2080,10 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G26" s="8">
         <v>480</v>
@@ -2071,7 +2095,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -2080,10 +2104,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -2092,10 +2116,10 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G27" s="8">
         <v>480</v>
@@ -2107,7 +2131,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -2116,10 +2140,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>15</v>
@@ -2128,13 +2152,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="G28" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
@@ -2143,7 +2167,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -2152,10 +2176,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -2164,13 +2188,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="G29" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>19</v>
@@ -2179,7 +2203,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -2188,10 +2212,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -2200,13 +2224,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="G30" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>19</v>
@@ -2215,7 +2239,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -2224,10 +2248,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -2236,13 +2260,13 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="G31" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>19</v>
@@ -2251,7 +2275,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -2272,13 +2296,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="G32" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>19</v>
@@ -2287,7 +2311,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -2296,10 +2320,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -2308,13 +2332,13 @@
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="G33" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>19</v>
@@ -2332,10 +2356,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2344,13 +2368,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G34" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -2359,7 +2383,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -2368,10 +2392,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2380,10 +2404,10 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G35" s="4">
         <v>480</v>
@@ -2395,7 +2419,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2404,10 +2428,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2416,13 +2440,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G36" s="4">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>19</v>
@@ -2431,7 +2455,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="4" t="s">
@@ -2440,10 +2464,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>102</v>
+        <v>42</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2452,13 +2476,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="G37" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>19</v>
@@ -2467,7 +2491,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2476,10 +2500,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2488,13 +2512,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="G38" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2503,7 +2527,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2512,10 +2536,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2524,10 +2548,10 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G39" s="4">
         <v>480</v>
@@ -2539,7 +2563,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2548,25 +2572,25 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="F40" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="G40" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>19</v>
@@ -2575,7 +2599,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2584,10 +2608,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2596,10 +2620,10 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="G41" s="4">
         <v>120</v>
@@ -2611,7 +2635,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2620,10 +2644,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2632,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="G42" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>19</v>
@@ -2647,7 +2671,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2656,10 +2680,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2668,13 +2692,13 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="G43" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>19</v>
@@ -2683,7 +2707,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2692,10 +2716,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
@@ -2704,13 +2728,13 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="G44" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>19</v>
@@ -2719,7 +2743,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2728,10 +2752,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2740,13 +2764,13 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="G45" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>19</v>
@@ -2755,7 +2779,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2764,10 +2788,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2776,13 +2800,13 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="G46" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>19</v>
@@ -2791,19 +2815,19 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2827,7 +2851,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="4" t="s">
@@ -2836,10 +2860,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2848,13 +2872,13 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="G48" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>19</v>
@@ -2863,7 +2887,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2884,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>37</v>
+        <v>125</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="G49" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>19</v>
@@ -2899,7 +2923,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2908,34 +2932,34 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="4">
+        <v>480</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="4">
-        <v>480</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2944,10 +2968,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
@@ -2956,10 +2980,10 @@
         <v>16</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G51" s="4">
         <v>480</v>
@@ -2980,10 +3004,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -2992,13 +3016,13 @@
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="G52" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>19</v>
@@ -3016,10 +3040,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>15</v>
@@ -3028,13 +3052,13 @@
         <v>16</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G53" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>19</v>
@@ -3052,10 +3076,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>15</v>
@@ -3064,13 +3088,13 @@
         <v>16</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="G54" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>19</v>
@@ -3079,7 +3103,7 @@
         <v>20</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="4" t="s">
@@ -3088,10 +3112,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -3100,10 +3124,10 @@
         <v>16</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="G55" s="4">
         <v>120</v>
@@ -3115,7 +3139,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="4" t="s">
@@ -3124,10 +3148,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -3136,10 +3160,10 @@
         <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G56" s="4">
         <v>480</v>
@@ -3151,7 +3175,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
@@ -3160,10 +3184,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -3172,13 +3196,13 @@
         <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="G57" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>19</v>
@@ -3187,7 +3211,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="4" t="s">
@@ -3196,10 +3220,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -3208,13 +3232,13 @@
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="G58" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>19</v>
@@ -3223,7 +3247,7 @@
         <v>20</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="4" t="s">
@@ -3232,34 +3256,34 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G59" s="4">
+        <v>120</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G59" s="4">
-        <v>480</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="4" t="s">
@@ -3268,25 +3292,25 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="F60" s="4" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="G60" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>19</v>
@@ -3295,7 +3319,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
@@ -3304,10 +3328,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3316,13 +3340,13 @@
         <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="G61" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>19</v>
@@ -3331,7 +3355,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="4" t="s">
@@ -3340,22 +3364,22 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G62" s="4">
         <v>480</v>
@@ -3367,7 +3391,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="4" t="s">
@@ -3376,10 +3400,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
@@ -3388,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="G63" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>19</v>
@@ -3403,19 +3427,21 @@
         <v>20</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K63" s="3"/>
+        <v>154</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="L63" s="4" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -3424,10 +3450,10 @@
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="G64" s="4">
         <v>480</v>
@@ -3439,19 +3465,19 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="4" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -3460,13 +3486,13 @@
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="G65" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>19</v>
@@ -3475,7 +3501,7 @@
         <v>20</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="4" t="s">
@@ -3484,10 +3510,10 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>15</v>
@@ -3496,13 +3522,13 @@
         <v>16</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G66" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>19</v>
@@ -3511,45 +3537,43 @@
         <v>20</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>157</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K66" s="3"/>
       <c r="L66" s="4" t="s">
-        <v>158</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G67" s="4">
+        <v>120</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G67" s="4">
-        <v>180</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="4" t="s">
@@ -3558,10 +3582,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
@@ -3570,13 +3594,13 @@
         <v>16</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>84</v>
+        <v>164</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="G68" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>19</v>
@@ -3585,19 +3609,19 @@
         <v>20</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="4" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
@@ -3606,10 +3630,10 @@
         <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G69" s="4">
         <v>480</v>
@@ -3621,7 +3645,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="s">
@@ -3630,10 +3654,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
@@ -3642,13 +3666,13 @@
         <v>16</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="G70" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>19</v>
@@ -3657,7 +3681,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="s">
@@ -3666,10 +3690,10 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>15</v>
@@ -3678,13 +3702,13 @@
         <v>16</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="G71" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>19</v>
@@ -3693,7 +3717,7 @@
         <v>20</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="4" t="s">
@@ -3702,10 +3726,10 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
@@ -3714,13 +3738,13 @@
         <v>16</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G72" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>19</v>
@@ -3729,7 +3753,7 @@
         <v>20</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="4" t="s">
@@ -3738,10 +3762,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -3750,13 +3774,13 @@
         <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>52</v>
+        <v>171</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="G73" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>19</v>
@@ -3765,7 +3789,7 @@
         <v>20</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="s">
@@ -3774,10 +3798,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -3786,13 +3810,13 @@
         <v>16</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="G74" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>19</v>
@@ -3801,7 +3825,7 @@
         <v>20</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="s">
@@ -3810,22 +3834,22 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G75" s="4">
         <v>480</v>
@@ -3837,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="s">
@@ -3846,10 +3870,10 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
@@ -3858,10 +3882,10 @@
         <v>16</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="G76" s="4">
         <v>90</v>
@@ -3873,7 +3897,7 @@
         <v>20</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="s">
@@ -3882,34 +3906,34 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G77" s="4">
+        <v>480</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="s">
@@ -3918,10 +3942,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
@@ -3930,10 +3954,10 @@
         <v>16</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="G78" s="4">
         <v>90</v>
@@ -3945,7 +3969,7 @@
         <v>20</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="K78" s="3"/>
       <c r="L78" s="4" t="s">
@@ -3954,10 +3978,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -3966,13 +3990,13 @@
         <v>16</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="G79" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>19</v>
@@ -3981,7 +4005,7 @@
         <v>20</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="s">
@@ -3990,10 +4014,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
@@ -4002,13 +4026,13 @@
         <v>16</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="G80" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>19</v>
@@ -4017,7 +4041,7 @@
         <v>20</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="s">
@@ -4026,10 +4050,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>15</v>
@@ -4038,10 +4062,10 @@
         <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G81" s="4">
         <v>480</v>
@@ -4053,7 +4077,7 @@
         <v>20</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="s">
@@ -4062,10 +4086,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
@@ -4074,10 +4098,10 @@
         <v>16</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G82" s="4">
         <v>480</v>
@@ -4089,7 +4113,7 @@
         <v>20</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="s">
@@ -4098,10 +4122,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
@@ -4110,13 +4134,13 @@
         <v>16</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="G83" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>19</v>
@@ -4125,7 +4149,7 @@
         <v>20</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="K83" s="3"/>
       <c r="L83" s="4" t="s">
@@ -4134,10 +4158,10 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>15</v>
@@ -4146,13 +4170,13 @@
         <v>16</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="G84" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>19</v>
@@ -4161,7 +4185,7 @@
         <v>20</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="s">
@@ -4170,10 +4194,10 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
@@ -4182,13 +4206,13 @@
         <v>16</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>186</v>
+        <v>53</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="G85" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>19</v>
@@ -4197,7 +4221,7 @@
         <v>20</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K85" s="3"/>
       <c r="L85" s="4" t="s">
@@ -4206,10 +4230,10 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>15</v>
@@ -4218,10 +4242,10 @@
         <v>16</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G86" s="4">
         <v>480</v>
@@ -4233,7 +4257,7 @@
         <v>20</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="s">
@@ -4242,10 +4266,10 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>15</v>
@@ -4254,10 +4278,10 @@
         <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="G87" s="4">
         <v>90</v>
@@ -4269,7 +4293,7 @@
         <v>20</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="s">
@@ -4278,10 +4302,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -4290,10 +4314,10 @@
         <v>16</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G88" s="4">
         <v>90</v>
@@ -4305,7 +4329,7 @@
         <v>20</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="s">
@@ -4314,10 +4338,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -4326,10 +4350,10 @@
         <v>16</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G89" s="4">
         <v>90</v>
@@ -4341,7 +4365,7 @@
         <v>20</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="s">
@@ -4350,10 +4374,10 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>15</v>
@@ -4362,13 +4386,13 @@
         <v>16</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G90" s="4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>19</v>
@@ -4377,7 +4401,7 @@
         <v>20</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="s">
@@ -4386,10 +4410,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>15</v>
@@ -4398,10 +4422,10 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G91" s="4">
         <v>90</v>
@@ -4413,7 +4437,7 @@
         <v>20</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="s">
@@ -4422,10 +4446,10 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>15</v>
@@ -4434,13 +4458,13 @@
         <v>16</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="G92" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>19</v>
@@ -4449,7 +4473,7 @@
         <v>20</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="4" t="s">
@@ -4458,10 +4482,10 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>15</v>
@@ -4470,10 +4494,10 @@
         <v>16</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G93" s="4">
         <v>480</v>
@@ -4485,7 +4509,7 @@
         <v>20</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="s">
@@ -4494,10 +4518,10 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>15</v>
@@ -4506,13 +4530,13 @@
         <v>16</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="G94" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>19</v>
@@ -4521,7 +4545,7 @@
         <v>20</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="4" t="s">
@@ -4530,10 +4554,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>15</v>
@@ -4542,10 +4566,10 @@
         <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G95" s="4">
         <v>90</v>
@@ -4557,7 +4581,7 @@
         <v>20</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="s">
@@ -4566,10 +4590,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>15</v>
@@ -4578,13 +4602,13 @@
         <v>16</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>28</v>
+        <v>208</v>
       </c>
       <c r="G96" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>19</v>
@@ -4593,7 +4617,7 @@
         <v>20</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="s">
@@ -4602,10 +4626,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>15</v>
@@ -4614,10 +4638,10 @@
         <v>16</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>104</v>
+        <v>200</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="G97" s="4">
         <v>90</v>
@@ -4629,7 +4653,7 @@
         <v>20</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="s">
@@ -4638,10 +4662,10 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>15</v>
@@ -4650,10 +4674,10 @@
         <v>16</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="G98" s="4">
         <v>90</v>
@@ -4665,7 +4689,7 @@
         <v>20</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="s">
@@ -4674,10 +4698,10 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>15</v>
@@ -4686,13 +4710,13 @@
         <v>16</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="G99" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>19</v>
@@ -4701,7 +4725,7 @@
         <v>20</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="s">
@@ -4710,10 +4734,10 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>15</v>
@@ -4722,13 +4746,13 @@
         <v>16</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>207</v>
+        <v>117</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="G100" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>19</v>
@@ -4737,19 +4761,19 @@
         <v>20</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>15</v>
@@ -4758,13 +4782,13 @@
         <v>16</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="G101" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>19</v>
@@ -4773,7 +4797,7 @@
         <v>20</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="s">
@@ -4782,10 +4806,10 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>15</v>
@@ -4794,13 +4818,13 @@
         <v>16</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>37</v>
+        <v>214</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="G102" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>19</v>
@@ -4809,7 +4833,7 @@
         <v>20</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="s">
@@ -4818,10 +4842,10 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>15</v>
@@ -4830,13 +4854,13 @@
         <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>215</v>
+        <v>53</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>216</v>
+        <v>54</v>
       </c>
       <c r="G103" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>19</v>
@@ -4845,7 +4869,7 @@
         <v>20</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="s">
@@ -4854,10 +4878,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>15</v>
@@ -4866,13 +4890,13 @@
         <v>16</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c r="G104" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>19</v>
@@ -4881,7 +4905,7 @@
         <v>20</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="s">
@@ -4890,10 +4914,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>15</v>
@@ -4902,13 +4926,13 @@
         <v>16</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>18</v>
+        <v>204</v>
       </c>
       <c r="G105" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>19</v>
@@ -4917,7 +4941,7 @@
         <v>20</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="4" t="s">
@@ -4926,25 +4950,25 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="F106" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="G106" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>19</v>
@@ -4953,7 +4977,7 @@
         <v>20</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="K106" s="3"/>
       <c r="L106" s="4" t="s">
@@ -4962,10 +4986,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>15</v>
@@ -4974,13 +4998,13 @@
         <v>16</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="G107" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>19</v>
@@ -4989,7 +5013,7 @@
         <v>20</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="s">
@@ -4998,25 +5022,25 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E108" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G108" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>19</v>
@@ -5025,7 +5049,7 @@
         <v>20</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="s">
@@ -5034,25 +5058,25 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F109" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E109" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G109" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>19</v>
@@ -5061,7 +5085,7 @@
         <v>20</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="s">
@@ -5070,10 +5094,10 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>15</v>
@@ -5082,13 +5106,13 @@
         <v>16</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="G110" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>19</v>
@@ -5097,7 +5121,7 @@
         <v>20</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="s">
@@ -5118,13 +5142,13 @@
         <v>16</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="G111" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>19</v>
@@ -5133,7 +5157,7 @@
         <v>20</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="s">
@@ -5142,10 +5166,10 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>228</v>
+        <v>158</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>15</v>
@@ -5154,10 +5178,10 @@
         <v>16</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G112" s="4">
         <v>90</v>
@@ -5169,7 +5193,7 @@
         <v>20</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="s">
@@ -5178,10 +5202,10 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>15</v>
@@ -5190,13 +5214,13 @@
         <v>16</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="G113" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>19</v>
@@ -5205,7 +5229,7 @@
         <v>20</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="s">
@@ -5214,10 +5238,10 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>15</v>
@@ -5226,13 +5250,13 @@
         <v>16</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="G114" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>19</v>
@@ -5241,7 +5265,7 @@
         <v>20</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="s">
@@ -5250,10 +5274,10 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>15</v>
@@ -5262,13 +5286,13 @@
         <v>16</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>203</v>
+        <v>59</v>
       </c>
       <c r="G115" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>19</v>
@@ -5277,7 +5301,7 @@
         <v>20</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="4" t="s">
@@ -5286,10 +5310,10 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>15</v>
@@ -5298,22 +5322,22 @@
         <v>16</v>
       </c>
       <c r="E116" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F116" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="G116" s="4">
+        <v>120</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J116" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="G116" s="4">
-        <v>90</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="s">
@@ -5322,10 +5346,10 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>15</v>
@@ -5334,10 +5358,10 @@
         <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G117" s="4">
         <v>90</v>
@@ -5349,7 +5373,7 @@
         <v>20</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="s">
@@ -5358,10 +5382,10 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>15</v>
@@ -5370,13 +5394,13 @@
         <v>16</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>197</v>
+        <v>31</v>
       </c>
       <c r="G118" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>19</v>
@@ -5385,7 +5409,7 @@
         <v>20</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="s">
@@ -5403,29 +5427,209 @@
         <v>15</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E119" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G119" s="4">
+        <v>480</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J119" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G119" s="4">
-        <v>90</v>
-      </c>
-      <c r="H119" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I119" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="K119" s="3"/>
       <c r="L119" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G120" s="4">
+        <v>480</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K120" s="3"/>
+      <c r="L120" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="4">
+        <v>480</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J121" s="3" t="s">
         <v>244</v>
+      </c>
+      <c r="K121" s="3"/>
+      <c r="L121" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G122" s="4">
+        <v>480</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K122" s="3"/>
+      <c r="L122" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G123" s="4">
+        <v>90</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K123" s="3"/>
+      <c r="L123" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G124" s="4">
+        <v>90</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K124" s="3"/>
+      <c r="L124" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,42 +58,177 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>10/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>10/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bobin</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>19/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>20/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>26/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca 2 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>19/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>27/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>09/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>12/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>26/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.   ca 3 </t>
+  </si>
+  <si>
+    <t>16/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>09/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>09/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
+  </si>
+  <si>
+    <t>19/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>19/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
     <t>02221908</t>
   </si>
   <si>
     <t>Nguyễn Minh Hoàng</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>19/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>20/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
+    <t>Tăng ca hỗ trợ lắp rack mobin</t>
   </si>
   <si>
     <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
   </si>
   <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>01921560</t>
-  </si>
-  <si>
-    <t>Trần Quang Hiệu</t>
-  </si>
-  <si>
     <t>12/09/2026 06:00:00</t>
   </si>
   <si>
@@ -103,106 +238,115 @@
     <t>tăng ca sản xuất ca 1</t>
   </si>
   <si>
-    <t>26/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>09/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 15:30:00</t>
+    <t>19/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
+  </si>
+  <si>
+    <t>15/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
+  </si>
+  <si>
+    <t>12/09/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>12/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 2</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>14/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 15:30:00</t>
   </si>
   <si>
     <t>tăng ca hỗ trợ kiểm kê tháng 9</t>
   </si>
   <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>14/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>11/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 16:00:00</t>
+    <t>26/09/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất :Ca 3</t>
+  </si>
+  <si>
+    <t>22/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:00:00</t>
   </si>
   <si>
     <t>tăng ca hỗ trợ lắp rack mobin</t>
   </si>
   <si>
-    <t>27/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>19/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>12/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>12/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng cường sản xuất </t>
-  </si>
-  <si>
-    <t>10/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>10/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ lắp rack mobin</t>
-  </si>
-  <si>
-    <t>12/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>19/09/2026 16:30:00</t>
+    <t>tăng ca sản xuất : ca 1</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>03/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>03/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
   </si>
   <si>
     <t>02224288</t>
@@ -211,6 +355,108 @@
     <t>Võ Văn Dương</t>
   </si>
   <si>
+    <t>21/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca lắp rack bonbin</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 2)</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>07/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>07/09/2026 18:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>17/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca1</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 2</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 2</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>17/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2026 16:00:00</t>
+  </si>
+  <si>
+    <t>lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
     <t>23/09/2026 14:00:00</t>
   </si>
   <si>
@@ -226,10 +472,238 @@
     <t>Từ chối</t>
   </si>
   <si>
-    <t>26/09/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 16:30:00</t>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca1 </t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất ( Ca 2 )</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>Tăng ca lắp rack xưởng 3</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca2</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>17/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>16/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>24/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>24/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất(ca2)</t>
+  </si>
+  <si>
+    <t>23/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>lắp rack bobin tại xưởng 3</t>
+  </si>
+  <si>
+    <t>22/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Hỗ trợ mở rộng sản xuất</t>
+  </si>
+  <si>
+    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>22/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
+  </si>
+  <si>
+    <t>15/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Kiểm kê hàng sản xuất</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>15/09/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
+  </si>
+  <si>
+    <t>25/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/09/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Kiểm kê kho tháng 9.</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>10/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>29/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>29/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>08/09/2026 19:30:00</t>
+  </si>
+  <si>
+    <t>28/09/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>28/09/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>16/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>18/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>15/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>14/09/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/09/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/09/2026 15:30:00</t>
   </si>
   <si>
     <t>01920862</t>
@@ -241,63 +715,6 @@
     <t>TĂNG CA SẢN XUẤT</t>
   </si>
   <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>15/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>18/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lắp rack xưởng 3 </t>
-  </si>
-  <si>
-    <t>13/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>26/09/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca2 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hỗ trợ kiểm kê tháng 9. </t>
-  </si>
-  <si>
-    <t>21/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bonbin</t>
-  </si>
-  <si>
     <t>02020497</t>
   </si>
   <si>
@@ -307,31 +724,7 @@
     <t>Tăng ca hổ trợ sản xuất (HC)</t>
   </si>
   <si>
-    <t>22/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca lắp rack bobin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.  ca1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất.   ca 3 </t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ca 3 tăng ca sản xuất. </t>
+    <t>kiểm kê</t>
   </si>
   <si>
     <t>02021131</t>
@@ -343,129 +736,21 @@
     <t xml:space="preserve">Tăng ca sản xuất </t>
   </si>
   <si>
-    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca3 </t>
-  </si>
-  <si>
-    <t>02325295</t>
-  </si>
-  <si>
-    <t>Lưu Văn Đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca  sản xuất  (ca 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca 2 tăng ca sản xuất. </t>
-  </si>
-  <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 2</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack bobin x3. </t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất :Ca 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền ca 2</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất : ca 1</t>
-  </si>
-  <si>
-    <t>03/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>03/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
     <t>02021742</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Dũng</t>
   </si>
   <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
     <t>tăng ca hỗ trợ sản xuất ca 2</t>
   </si>
   <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất(ca 3)</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>Thực hiện dự án cải tiến</t>
-  </si>
-  <si>
     <t>tăng ca hỗ trợ sản xuất ca 3</t>
   </si>
   <si>
-    <t>Hỗ trợ sản xuất(ca 2)</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>thực hiện dự án cải tiến</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>17/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:00:00</t>
-  </si>
-  <si>
-    <t>lắp rack xưởng 3</t>
-  </si>
-  <si>
     <t>02022149</t>
   </si>
   <si>
@@ -478,27 +763,12 @@
     <t>Nguyễn Công Hậu</t>
   </si>
   <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 2)</t>
+  </si>
+  <si>
     <t>tăng ca hỗ trợ sản xuất (ca3)</t>
   </si>
   <si>
-    <t>tăng ca hỗ trợ sản xuất (ca 2)</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>09/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>09/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (HC)</t>
-  </si>
-  <si>
     <t>tăng ca hỗ trợ sản xuất ( ca 1)</t>
   </si>
   <si>
@@ -511,277 +781,28 @@
     <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
   </si>
   <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>Tăng ca lắp rack xưởng 3</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>23/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>Tăng ca sản xuất ( Ca 2 )</t>
-  </si>
-  <si>
-    <t>24/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>24/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất(ca2)</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền ( Ca 1 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca lắp rack xưởng 3 </t>
-  </si>
-  <si>
     <t>02645250</t>
   </si>
   <si>
     <t>Trần Xuân Bắc</t>
   </si>
   <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ nghiền CA 3</t>
+  </si>
+  <si>
     <t>Tăng ca hỗ trợ nghiền.</t>
   </si>
   <si>
-    <t>17/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>lắp Rack tại xưởng 3, chuẩn bị sản xuất line 21, 01</t>
-  </si>
-  <si>
-    <t>22/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>lắp rack bobin tại xưởng 3</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>22/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>22/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack Bobbin mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>28/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>28/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ nghiền </t>
-  </si>
-  <si>
-    <t>Hỗ trợ mở rộng sản xuất</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tăng ca thứ 7 </t>
   </si>
   <si>
-    <t>Hỗ trợ lắp đặt rack mở rộng sản xuất.</t>
-  </si>
-  <si>
-    <t>Tăng ca vệ sinh máy PL24 test vật liệu mới.</t>
-  </si>
-  <si>
-    <t>16/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>16/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ nghiền CA 3</t>
-  </si>
-  <si>
-    <t>18/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>18/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2026 15:30:00</t>
-  </si>
-  <si>
     <t>17/09/2026 20:30:00</t>
   </si>
   <si>
     <t>17/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>21/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Kiểm kê kho tháng 9.</t>
-  </si>
-  <si>
-    <t>15/09/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>17/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>17/09/2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>08/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>08/09/2026 19:30:00</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>15/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>15/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>11/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>10/09/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 20:30:00</t>
-  </si>
-  <si>
-    <t>14/09/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>07/09/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>07/09/2026 18:30:00</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 2</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
-  </si>
-  <si>
-    <t>02223535</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca3 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca1 </t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca2</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1285,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -1345,7 +1366,7 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
@@ -1354,10 +1375,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>15</v>
@@ -1366,10 +1387,10 @@
         <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G6" s="8">
         <v>480</v>
@@ -1381,7 +1402,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -1390,10 +1411,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
@@ -1402,10 +1423,10 @@
         <v>16</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="G7" s="8">
         <v>480</v>
@@ -1417,7 +1438,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -1438,13 +1459,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G8" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>19</v>
@@ -1453,7 +1474,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1462,10 +1483,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
@@ -1474,13 +1495,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>19</v>
@@ -1489,7 +1510,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1498,10 +1519,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
@@ -1510,13 +1531,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
@@ -1525,7 +1546,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
@@ -1534,10 +1555,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>15</v>
@@ -1546,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8">
         <v>480</v>
@@ -1561,7 +1582,7 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
@@ -1570,23 +1591,23 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="G12" s="8">
         <v>480</v>
       </c>
@@ -1597,7 +1618,7 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
@@ -1606,11 +1627,11 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
       </c>
@@ -1618,10 +1639,10 @@
         <v>16</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G13" s="8">
         <v>120</v>
@@ -1633,7 +1654,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1642,25 +1663,25 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G14" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>19</v>
@@ -1669,7 +1690,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
@@ -1678,10 +1699,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
@@ -1690,13 +1711,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G15" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>19</v>
@@ -1705,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
@@ -1714,22 +1735,22 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G16" s="8">
         <v>480</v>
@@ -1741,7 +1762,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1750,25 +1771,25 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G17" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>19</v>
@@ -1777,7 +1798,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
@@ -1786,10 +1807,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -1798,13 +1819,13 @@
         <v>16</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G18" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>19</v>
@@ -1813,33 +1834,31 @@
         <v>20</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>67</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="K18" s="7"/>
       <c r="L18" s="8" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="8">
         <v>480</v>
@@ -1851,7 +1870,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
@@ -1860,10 +1879,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
@@ -1872,10 +1891,10 @@
         <v>16</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="G20" s="8">
         <v>480</v>
@@ -1887,7 +1906,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
@@ -1896,10 +1915,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
@@ -1908,10 +1927,10 @@
         <v>16</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G21" s="8">
         <v>480</v>
@@ -1923,7 +1942,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
@@ -1932,10 +1951,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
@@ -1944,10 +1963,10 @@
         <v>16</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G22" s="8">
         <v>120</v>
@@ -1959,7 +1978,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
@@ -1968,10 +1987,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
@@ -1980,13 +1999,13 @@
         <v>16</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="G23" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>19</v>
@@ -1995,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
@@ -2004,10 +2023,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
@@ -2016,10 +2035,10 @@
         <v>16</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G24" s="8">
         <v>480</v>
@@ -2031,7 +2050,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -2040,25 +2059,25 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G25" s="8">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
@@ -2067,7 +2086,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
@@ -2076,10 +2095,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
@@ -2088,10 +2107,10 @@
         <v>16</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="G26" s="8">
         <v>480</v>
@@ -2103,7 +2122,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -2112,10 +2131,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>15</v>
@@ -2124,10 +2143,10 @@
         <v>16</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="G27" s="8">
         <v>480</v>
@@ -2139,7 +2158,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="8" t="s">
@@ -2148,22 +2167,22 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="G28" s="8">
         <v>480</v>
@@ -2175,7 +2194,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
@@ -2184,10 +2203,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -2196,13 +2215,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="G29" s="8">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>19</v>
@@ -2211,7 +2230,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -2220,10 +2239,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -2232,13 +2251,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G30" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>19</v>
@@ -2247,7 +2266,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -2256,10 +2275,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -2268,10 +2287,10 @@
         <v>16</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="G31" s="4">
         <v>480</v>
@@ -2283,7 +2302,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
@@ -2292,10 +2311,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>15</v>
@@ -2304,14 +2323,14 @@
         <v>16</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="4">
         <v>90</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="4">
-        <v>120</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>19</v>
       </c>
@@ -2319,7 +2338,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="4" t="s">
@@ -2328,34 +2347,34 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="4">
+        <v>90</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G33" s="4">
-        <v>480</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="4" t="s">
@@ -2364,10 +2383,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>15</v>
@@ -2376,13 +2395,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="G34" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>19</v>
@@ -2391,7 +2410,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="4" t="s">
@@ -2400,10 +2419,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>15</v>
@@ -2412,10 +2431,10 @@
         <v>16</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G35" s="4">
         <v>480</v>
@@ -2427,7 +2446,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="4" t="s">
@@ -2436,10 +2455,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -2448,10 +2467,10 @@
         <v>16</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G36" s="4">
         <v>480</v>
@@ -2472,10 +2491,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -2484,13 +2503,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="G37" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>19</v>
@@ -2499,7 +2518,7 @@
         <v>20</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="4" t="s">
@@ -2508,10 +2527,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -2520,13 +2539,13 @@
         <v>16</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="G38" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>19</v>
@@ -2535,7 +2554,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="4" t="s">
@@ -2544,10 +2563,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -2556,10 +2575,10 @@
         <v>16</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G39" s="4">
         <v>480</v>
@@ -2571,7 +2590,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="4" t="s">
@@ -2580,10 +2599,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -2592,10 +2611,10 @@
         <v>16</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G40" s="4">
         <v>480</v>
@@ -2607,7 +2626,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="4" t="s">
@@ -2616,10 +2635,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -2628,10 +2647,10 @@
         <v>16</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G41" s="4">
         <v>480</v>
@@ -2643,7 +2662,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="4" t="s">
@@ -2652,10 +2671,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>15</v>
@@ -2664,10 +2683,10 @@
         <v>16</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="G42" s="4">
         <v>480</v>
@@ -2679,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
@@ -2688,10 +2707,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>15</v>
@@ -2700,10 +2719,10 @@
         <v>16</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="G43" s="4">
         <v>480</v>
@@ -2715,7 +2734,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
@@ -2724,10 +2743,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
@@ -2736,13 +2755,13 @@
         <v>16</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="G44" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>19</v>
@@ -2751,7 +2770,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
@@ -2760,10 +2779,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
@@ -2772,13 +2791,13 @@
         <v>16</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="G45" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>19</v>
@@ -2787,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
@@ -2796,10 +2815,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>15</v>
@@ -2808,13 +2827,13 @@
         <v>16</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="G46" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>19</v>
@@ -2823,7 +2842,7 @@
         <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="4" t="s">
@@ -2832,10 +2851,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -2844,10 +2863,10 @@
         <v>16</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G47" s="4">
         <v>480</v>
@@ -2868,10 +2887,10 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>15</v>
@@ -2880,13 +2899,13 @@
         <v>16</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="G48" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>19</v>
@@ -2895,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="4" t="s">
@@ -2904,10 +2923,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>15</v>
@@ -2916,11 +2935,11 @@
         <v>16</v>
       </c>
       <c r="E49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="G49" s="4">
         <v>480</v>
       </c>
@@ -2931,7 +2950,7 @@
         <v>20</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="4" t="s">
@@ -2940,10 +2959,10 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>15</v>
@@ -2952,10 +2971,10 @@
         <v>16</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G50" s="4">
         <v>480</v>
@@ -2967,7 +2986,7 @@
         <v>20</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="4" t="s">
@@ -2976,10 +2995,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>15</v>
@@ -3003,7 +3022,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="4" t="s">
@@ -3012,10 +3031,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>15</v>
@@ -3024,10 +3043,10 @@
         <v>16</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="G52" s="4">
         <v>480</v>
@@ -3039,7 +3058,7 @@
         <v>20</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="4" t="s">
@@ -3048,34 +3067,34 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G53" s="4">
+        <v>480</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G53" s="4">
-        <v>480</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="4" t="s">
@@ -3096,10 +3115,10 @@
         <v>16</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="G54" s="4">
         <v>480</v>
@@ -3120,10 +3139,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>15</v>
@@ -3132,10 +3151,10 @@
         <v>16</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G55" s="4">
         <v>480</v>
@@ -3147,7 +3166,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="4" t="s">
@@ -3156,10 +3175,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>15</v>
@@ -3168,13 +3187,13 @@
         <v>16</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G56" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>19</v>
@@ -3183,7 +3202,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="4" t="s">
@@ -3192,10 +3211,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>15</v>
@@ -3204,10 +3223,10 @@
         <v>16</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G57" s="4">
         <v>480</v>
@@ -3219,7 +3238,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="4" t="s">
@@ -3228,10 +3247,10 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>15</v>
@@ -3240,13 +3259,13 @@
         <v>16</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="G58" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>19</v>
@@ -3255,7 +3274,7 @@
         <v>20</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="4" t="s">
@@ -3264,10 +3283,10 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>15</v>
@@ -3276,10 +3295,10 @@
         <v>16</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G59" s="4">
         <v>480</v>
@@ -3291,7 +3310,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="4" t="s">
@@ -3300,10 +3319,10 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>15</v>
@@ -3312,13 +3331,13 @@
         <v>16</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="G60" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>19</v>
@@ -3327,7 +3346,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="4" t="s">
@@ -3336,10 +3355,10 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>15</v>
@@ -3348,10 +3367,10 @@
         <v>16</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G61" s="4">
         <v>480</v>
@@ -3363,7 +3382,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="4" t="s">
@@ -3372,10 +3391,10 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>15</v>
@@ -3384,13 +3403,13 @@
         <v>16</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G62" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>19</v>
@@ -3408,10 +3427,10 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>15</v>
@@ -3420,10 +3439,10 @@
         <v>16</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G63" s="4">
         <v>480</v>
@@ -3435,7 +3454,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="4" t="s">
@@ -3444,10 +3463,10 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>15</v>
@@ -3456,10 +3475,10 @@
         <v>16</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G64" s="4">
         <v>480</v>
@@ -3471,7 +3490,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="4" t="s">
@@ -3480,10 +3499,10 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>15</v>
@@ -3492,13 +3511,13 @@
         <v>16</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="G65" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>19</v>
@@ -3507,19 +3526,21 @@
         <v>20</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K65" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="L65" s="4" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>15</v>
@@ -3528,10 +3549,10 @@
         <v>16</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G66" s="4">
         <v>480</v>
@@ -3543,7 +3564,7 @@
         <v>20</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="4" t="s">
@@ -3552,10 +3573,10 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>15</v>
@@ -3564,10 +3585,10 @@
         <v>16</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="G67" s="4">
         <v>480</v>
@@ -3579,7 +3600,7 @@
         <v>20</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="4" t="s">
@@ -3588,10 +3609,10 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>15</v>
@@ -3600,13 +3621,13 @@
         <v>16</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>28</v>
+        <v>137</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="G68" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>19</v>
@@ -3615,7 +3636,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="4" t="s">
@@ -3624,10 +3645,10 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
@@ -3636,13 +3657,13 @@
         <v>16</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="G69" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>19</v>
@@ -3651,7 +3672,7 @@
         <v>20</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="4" t="s">
@@ -3660,10 +3681,10 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>15</v>
@@ -3672,10 +3693,10 @@
         <v>16</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G70" s="4">
         <v>480</v>
@@ -3687,7 +3708,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="K70" s="3"/>
       <c r="L70" s="4" t="s">
@@ -3696,10 +3717,10 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>15</v>
@@ -3708,13 +3729,13 @@
         <v>16</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="G71" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>19</v>
@@ -3723,7 +3744,7 @@
         <v>20</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="K71" s="3"/>
       <c r="L71" s="4" t="s">
@@ -3732,10 +3753,10 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>15</v>
@@ -3744,13 +3765,13 @@
         <v>16</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="G72" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>19</v>
@@ -3759,7 +3780,7 @@
         <v>20</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="K72" s="3"/>
       <c r="L72" s="4" t="s">
@@ -3768,10 +3789,10 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>15</v>
@@ -3780,10 +3801,10 @@
         <v>16</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G73" s="4">
         <v>480</v>
@@ -3795,7 +3816,7 @@
         <v>20</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="K73" s="3"/>
       <c r="L73" s="4" t="s">
@@ -3804,10 +3825,10 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>15</v>
@@ -3816,10 +3837,10 @@
         <v>16</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G74" s="4">
         <v>480</v>
@@ -3831,7 +3852,7 @@
         <v>20</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="K74" s="3"/>
       <c r="L74" s="4" t="s">
@@ -3840,10 +3861,10 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>15</v>
@@ -3852,10 +3873,10 @@
         <v>16</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="G75" s="4">
         <v>480</v>
@@ -3867,7 +3888,7 @@
         <v>20</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K75" s="3"/>
       <c r="L75" s="4" t="s">
@@ -3876,10 +3897,10 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>15</v>
@@ -3888,13 +3909,13 @@
         <v>16</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="G76" s="4">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>19</v>
@@ -3903,7 +3924,7 @@
         <v>20</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K76" s="3"/>
       <c r="L76" s="4" t="s">
@@ -3924,10 +3945,10 @@
         <v>16</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G77" s="4">
         <v>480</v>
@@ -3939,7 +3960,7 @@
         <v>20</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K77" s="3"/>
       <c r="L77" s="4" t="s">
@@ -3948,10 +3969,10 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
@@ -3960,10 +3981,10 @@
         <v>16</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="G78" s="4">
         <v>480</v>
@@ -3984,10 +4005,10 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>15</v>
@@ -3996,13 +4017,13 @@
         <v>16</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G79" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>19</v>
@@ -4011,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="K79" s="3"/>
       <c r="L79" s="4" t="s">
@@ -4020,10 +4041,10 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>15</v>
@@ -4032,10 +4053,10 @@
         <v>16</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G80" s="4">
         <v>480</v>
@@ -4047,7 +4068,7 @@
         <v>20</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="K80" s="3"/>
       <c r="L80" s="4" t="s">
@@ -4056,10 +4077,10 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>15</v>
@@ -4068,13 +4089,13 @@
         <v>16</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G81" s="4">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>19</v>
@@ -4083,7 +4104,7 @@
         <v>20</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K81" s="3"/>
       <c r="L81" s="4" t="s">
@@ -4092,10 +4113,10 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>15</v>
@@ -4104,10 +4125,10 @@
         <v>16</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G82" s="4">
         <v>480</v>
@@ -4119,7 +4140,7 @@
         <v>20</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K82" s="3"/>
       <c r="L82" s="4" t="s">
@@ -4128,10 +4149,10 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>15</v>
@@ -4140,10 +4161,10 @@
         <v>16</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="G83" s="4">
         <v>90</v>
@@ -4164,34 +4185,34 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" s="4">
+        <v>480</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G84" s="4">
-        <v>90</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="K84" s="3"/>
       <c r="L84" s="4" t="s">
@@ -4200,10 +4221,10 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>15</v>
@@ -4212,13 +4233,13 @@
         <v>16</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="G85" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>19</v>
@@ -4236,10 +4257,10 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>15</v>
@@ -4251,7 +4272,7 @@
         <v>172</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="G86" s="4">
         <v>90</v>
@@ -4263,7 +4284,7 @@
         <v>20</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K86" s="3"/>
       <c r="L86" s="4" t="s">
@@ -4272,10 +4293,10 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>15</v>
@@ -4284,13 +4305,13 @@
         <v>16</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="G87" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>19</v>
@@ -4299,7 +4320,7 @@
         <v>20</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="K87" s="3"/>
       <c r="L87" s="4" t="s">
@@ -4308,10 +4329,10 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>15</v>
@@ -4320,11 +4341,11 @@
         <v>16</v>
       </c>
       <c r="E88" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="G88" s="4">
         <v>480</v>
       </c>
@@ -4335,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K88" s="3"/>
       <c r="L88" s="4" t="s">
@@ -4344,10 +4365,10 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>15</v>
@@ -4356,13 +4377,13 @@
         <v>16</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>147</v>
+        <v>25</v>
       </c>
       <c r="G89" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>19</v>
@@ -4371,7 +4392,7 @@
         <v>20</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K89" s="3"/>
       <c r="L89" s="4" t="s">
@@ -4380,25 +4401,25 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="G90" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>19</v>
@@ -4407,7 +4428,7 @@
         <v>20</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K90" s="3"/>
       <c r="L90" s="4" t="s">
@@ -4416,10 +4437,10 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>15</v>
@@ -4428,13 +4449,13 @@
         <v>16</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G91" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>19</v>
@@ -4443,7 +4464,7 @@
         <v>20</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K91" s="3"/>
       <c r="L91" s="4" t="s">
@@ -4452,25 +4473,25 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>180</v>
+        <v>59</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="G92" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>19</v>
@@ -4479,7 +4500,7 @@
         <v>20</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="K92" s="3"/>
       <c r="L92" s="4" t="s">
@@ -4488,10 +4509,10 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>15</v>
@@ -4500,10 +4521,10 @@
         <v>16</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>48</v>
+        <v>183</v>
       </c>
       <c r="G93" s="4">
         <v>90</v>
@@ -4515,7 +4536,7 @@
         <v>20</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K93" s="3"/>
       <c r="L93" s="4" t="s">
@@ -4524,25 +4545,25 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>16</v>
+        <v>181</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G94" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>19</v>
@@ -4551,7 +4572,7 @@
         <v>20</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K94" s="3"/>
       <c r="L94" s="4" t="s">
@@ -4560,10 +4581,10 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>15</v>
@@ -4572,10 +4593,10 @@
         <v>16</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G95" s="4">
         <v>480</v>
@@ -4587,7 +4608,7 @@
         <v>20</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="K95" s="3"/>
       <c r="L95" s="4" t="s">
@@ -4596,22 +4617,22 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G96" s="4">
         <v>480</v>
@@ -4623,7 +4644,7 @@
         <v>20</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K96" s="3"/>
       <c r="L96" s="4" t="s">
@@ -4632,10 +4653,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>15</v>
@@ -4644,10 +4665,10 @@
         <v>16</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G97" s="4">
         <v>90</v>
@@ -4659,7 +4680,7 @@
         <v>20</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="K97" s="3"/>
       <c r="L97" s="4" t="s">
@@ -4668,25 +4689,25 @@
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
       <c r="G98" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>19</v>
@@ -4695,7 +4716,7 @@
         <v>20</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K98" s="3"/>
       <c r="L98" s="4" t="s">
@@ -4704,10 +4725,10 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>15</v>
@@ -4716,10 +4737,10 @@
         <v>16</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G99" s="4">
         <v>90</v>
@@ -4731,19 +4752,19 @@
         <v>20</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="4" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>15</v>
@@ -4752,10 +4773,10 @@
         <v>16</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="G100" s="4">
         <v>90</v>
@@ -4767,7 +4788,7 @@
         <v>20</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="K100" s="3"/>
       <c r="L100" s="4" t="s">
@@ -4776,10 +4797,10 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>15</v>
@@ -4788,13 +4809,13 @@
         <v>16</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G101" s="4">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>19</v>
@@ -4803,7 +4824,7 @@
         <v>20</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="4" t="s">
@@ -4812,10 +4833,10 @@
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>15</v>
@@ -4824,13 +4845,13 @@
         <v>16</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="G102" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>19</v>
@@ -4839,7 +4860,7 @@
         <v>20</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="K102" s="3"/>
       <c r="L102" s="4" t="s">
@@ -4848,10 +4869,10 @@
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>15</v>
@@ -4860,13 +4881,13 @@
         <v>16</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>60</v>
+        <v>202</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>61</v>
+        <v>203</v>
       </c>
       <c r="G103" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>19</v>
@@ -4875,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="4" t="s">
@@ -4884,10 +4905,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>15</v>
@@ -4896,13 +4917,13 @@
         <v>16</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="G104" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>19</v>
@@ -4911,7 +4932,7 @@
         <v>20</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K104" s="3"/>
       <c r="L104" s="4" t="s">
@@ -4920,10 +4941,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>15</v>
@@ -4932,10 +4953,10 @@
         <v>16</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G105" s="4">
         <v>90</v>
@@ -4947,7 +4968,7 @@
         <v>20</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="4" t="s">
@@ -4956,10 +4977,10 @@
     </row>
     <row r="106">
       <c r="A106" s="3" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>15</v>
@@ -4968,13 +4989,13 @@
         <v>16</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="G106" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>19</v>
@@ -4983,7 +5004,7 @@
         <v>20</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="K106" s="3"/>
       <c r="L106" s="4" t="s">
@@ -4992,10 +5013,10 @@
     </row>
     <row r="107">
       <c r="A107" s="3" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>15</v>
@@ -5004,10 +5025,10 @@
         <v>16</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G107" s="4">
         <v>90</v>
@@ -5019,19 +5040,19 @@
         <v>20</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K107" s="3"/>
       <c r="L107" s="4" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>15</v>
@@ -5040,10 +5061,10 @@
         <v>16</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="G108" s="4">
         <v>90</v>
@@ -5055,19 +5076,19 @@
         <v>20</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="K108" s="3"/>
       <c r="L108" s="4" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>15</v>
@@ -5076,13 +5097,13 @@
         <v>16</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G109" s="4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>19</v>
@@ -5091,7 +5112,7 @@
         <v>20</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="4" t="s">
@@ -5100,10 +5121,10 @@
     </row>
     <row r="110">
       <c r="A110" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>15</v>
@@ -5112,13 +5133,13 @@
         <v>16</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="G110" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>19</v>
@@ -5127,7 +5148,7 @@
         <v>20</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="K110" s="3"/>
       <c r="L110" s="4" t="s">
@@ -5136,10 +5157,10 @@
     </row>
     <row r="111">
       <c r="A111" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>15</v>
@@ -5148,10 +5169,10 @@
         <v>16</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G111" s="4">
         <v>90</v>
@@ -5163,7 +5184,7 @@
         <v>20</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K111" s="3"/>
       <c r="L111" s="4" t="s">
@@ -5172,10 +5193,10 @@
     </row>
     <row r="112">
       <c r="A112" s="3" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>15</v>
@@ -5184,13 +5205,13 @@
         <v>16</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G112" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>19</v>
@@ -5199,7 +5220,7 @@
         <v>20</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="K112" s="3"/>
       <c r="L112" s="4" t="s">
@@ -5208,10 +5229,10 @@
     </row>
     <row r="113">
       <c r="A113" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>15</v>
@@ -5235,7 +5256,7 @@
         <v>20</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K113" s="3"/>
       <c r="L113" s="4" t="s">
@@ -5244,10 +5265,10 @@
     </row>
     <row r="114">
       <c r="A114" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>15</v>
@@ -5256,13 +5277,13 @@
         <v>16</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="G114" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>19</v>
@@ -5271,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K114" s="3"/>
       <c r="L114" s="4" t="s">
@@ -5280,10 +5301,10 @@
     </row>
     <row r="115">
       <c r="A115" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>15</v>
@@ -5292,10 +5313,10 @@
         <v>16</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="G115" s="4">
         <v>90</v>
@@ -5307,7 +5328,7 @@
         <v>20</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="4" t="s">
@@ -5316,10 +5337,10 @@
     </row>
     <row r="116">
       <c r="A116" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>15</v>
@@ -5328,13 +5349,13 @@
         <v>16</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>221</v>
+        <v>25</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>222</v>
+        <v>26</v>
       </c>
       <c r="G116" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>19</v>
@@ -5343,7 +5364,7 @@
         <v>20</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K116" s="3"/>
       <c r="L116" s="4" t="s">
@@ -5352,10 +5373,10 @@
     </row>
     <row r="117">
       <c r="A117" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>15</v>
@@ -5364,10 +5385,10 @@
         <v>16</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G117" s="4">
         <v>90</v>
@@ -5379,7 +5400,7 @@
         <v>20</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="4" t="s">
@@ -5388,10 +5409,10 @@
     </row>
     <row r="118">
       <c r="A118" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>15</v>
@@ -5400,13 +5421,13 @@
         <v>16</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="G118" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>19</v>
@@ -5415,7 +5436,7 @@
         <v>20</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="K118" s="3"/>
       <c r="L118" s="4" t="s">
@@ -5424,10 +5445,10 @@
     </row>
     <row r="119">
       <c r="A119" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>15</v>
@@ -5436,13 +5457,13 @@
         <v>16</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G119" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>19</v>
@@ -5451,7 +5472,7 @@
         <v>20</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="K119" s="3"/>
       <c r="L119" s="4" t="s">
@@ -5460,10 +5481,10 @@
     </row>
     <row r="120">
       <c r="A120" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>15</v>
@@ -5472,13 +5493,13 @@
         <v>16</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="G120" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>19</v>
@@ -5487,7 +5508,7 @@
         <v>20</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="K120" s="3"/>
       <c r="L120" s="4" t="s">
@@ -5496,10 +5517,10 @@
     </row>
     <row r="121">
       <c r="A121" s="3" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>15</v>
@@ -5508,10 +5529,10 @@
         <v>16</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G121" s="4">
         <v>480</v>
@@ -5523,7 +5544,7 @@
         <v>20</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="K121" s="3"/>
       <c r="L121" s="4" t="s">
@@ -5532,10 +5553,10 @@
     </row>
     <row r="122">
       <c r="A122" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>15</v>
@@ -5544,10 +5565,10 @@
         <v>16</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="G122" s="4">
         <v>90</v>
@@ -5559,7 +5580,7 @@
         <v>20</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="K122" s="3"/>
       <c r="L122" s="4" t="s">
@@ -5568,10 +5589,10 @@
     </row>
     <row r="123">
       <c r="A123" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>15</v>
@@ -5580,10 +5601,10 @@
         <v>16</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="G123" s="4">
         <v>90</v>
@@ -5595,7 +5616,7 @@
         <v>20</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="K123" s="3"/>
       <c r="L123" s="4" t="s">
@@ -5604,10 +5625,10 @@
     </row>
     <row r="124">
       <c r="A124" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>15</v>
@@ -5616,10 +5637,10 @@
         <v>16</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G124" s="4">
         <v>480</v>
@@ -5631,7 +5652,7 @@
         <v>20</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K124" s="3"/>
       <c r="L124" s="4" t="s">
@@ -5640,10 +5661,10 @@
     </row>
     <row r="125">
       <c r="A125" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>15</v>
@@ -5652,10 +5673,10 @@
         <v>16</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G125" s="4">
         <v>480</v>
@@ -5667,7 +5688,7 @@
         <v>20</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K125" s="3"/>
       <c r="L125" s="4" t="s">
@@ -5676,10 +5697,10 @@
     </row>
     <row r="126">
       <c r="A126" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>15</v>
@@ -5688,13 +5709,13 @@
         <v>16</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>226</v>
+        <v>71</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>227</v>
+        <v>45</v>
       </c>
       <c r="G126" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>19</v>
@@ -5703,7 +5724,7 @@
         <v>20</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="K126" s="3"/>
       <c r="L126" s="4" t="s">
@@ -5712,10 +5733,10 @@
     </row>
     <row r="127">
       <c r="A127" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>15</v>
@@ -5724,13 +5745,13 @@
         <v>16</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>228</v>
+        <v>48</v>
       </c>
       <c r="G127" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>19</v>
@@ -5739,7 +5760,7 @@
         <v>20</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="K127" s="3"/>
       <c r="L127" s="4" t="s">
@@ -5748,10 +5769,10 @@
     </row>
     <row r="128">
       <c r="A128" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>15</v>
@@ -5760,11 +5781,11 @@
         <v>16</v>
       </c>
       <c r="E128" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F128" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F128" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="G128" s="4">
         <v>480</v>
       </c>
@@ -5775,7 +5796,7 @@
         <v>20</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="K128" s="3"/>
       <c r="L128" s="4" t="s">
@@ -5784,10 +5805,10 @@
     </row>
     <row r="129">
       <c r="A129" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>15</v>
@@ -5796,10 +5817,10 @@
         <v>16</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="G129" s="4">
         <v>90</v>
@@ -5811,19 +5832,19 @@
         <v>20</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="K129" s="3"/>
       <c r="L129" s="4" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>15</v>
@@ -5832,13 +5853,13 @@
         <v>16</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>233</v>
+        <v>25</v>
       </c>
       <c r="G130" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H130" s="3" t="s">
         <v>19</v>
@@ -5847,7 +5868,7 @@
         <v>20</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="K130" s="3"/>
       <c r="L130" s="4" t="s">
@@ -5856,10 +5877,10 @@
     </row>
     <row r="131">
       <c r="A131" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>15</v>
@@ -5868,13 +5889,13 @@
         <v>16</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>157</v>
+        <v>94</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="G131" s="4">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>19</v>
@@ -5883,7 +5904,7 @@
         <v>20</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K131" s="3"/>
       <c r="L131" s="4" t="s">
@@ -5892,10 +5913,10 @@
     </row>
     <row r="132">
       <c r="A132" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>15</v>
@@ -5904,13 +5925,13 @@
         <v>16</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>219</v>
+        <v>33</v>
       </c>
       <c r="G132" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H132" s="3" t="s">
         <v>19</v>
@@ -5919,7 +5940,7 @@
         <v>20</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K132" s="3"/>
       <c r="L132" s="4" t="s">
@@ -5928,10 +5949,10 @@
     </row>
     <row r="133">
       <c r="A133" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>15</v>
@@ -5940,10 +5961,10 @@
         <v>16</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G133" s="4">
         <v>480</v>
@@ -5955,7 +5976,7 @@
         <v>20</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K133" s="3"/>
       <c r="L133" s="4" t="s">
@@ -5964,10 +5985,10 @@
     </row>
     <row r="134">
       <c r="A134" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>15</v>
@@ -5976,10 +5997,10 @@
         <v>16</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="G134" s="4">
         <v>480</v>
@@ -5991,7 +6012,7 @@
         <v>20</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="K134" s="3"/>
       <c r="L134" s="4" t="s">
@@ -6000,10 +6021,10 @@
     </row>
     <row r="135">
       <c r="A135" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>15</v>
@@ -6012,10 +6033,10 @@
         <v>16</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="G135" s="4">
         <v>480</v>
@@ -6027,7 +6048,7 @@
         <v>20</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>238</v>
+        <v>38</v>
       </c>
       <c r="K135" s="3"/>
       <c r="L135" s="4" t="s">
@@ -6036,10 +6057,10 @@
     </row>
     <row r="136">
       <c r="A136" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>15</v>
@@ -6048,13 +6069,13 @@
         <v>16</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>239</v>
+        <v>94</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="G136" s="4">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="H136" s="3" t="s">
         <v>19</v>
@@ -6063,7 +6084,7 @@
         <v>20</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="K136" s="3"/>
       <c r="L136" s="4" t="s">
@@ -6072,10 +6093,10 @@
     </row>
     <row r="137">
       <c r="A137" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>15</v>
@@ -6084,10 +6105,10 @@
         <v>16</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="G137" s="4">
         <v>480</v>
@@ -6099,7 +6120,7 @@
         <v>20</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>243</v>
+        <v>38</v>
       </c>
       <c r="K137" s="3"/>
       <c r="L137" s="4" t="s">
@@ -6108,10 +6129,10 @@
     </row>
     <row r="138">
       <c r="A138" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>15</v>
@@ -6135,7 +6156,7 @@
         <v>20</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K138" s="3"/>
       <c r="L138" s="4" t="s">
@@ -6144,10 +6165,10 @@
     </row>
     <row r="139">
       <c r="A139" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>15</v>
@@ -6156,11 +6177,11 @@
         <v>16</v>
       </c>
       <c r="E139" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F139" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="G139" s="4">
         <v>480</v>
       </c>
@@ -6171,7 +6192,7 @@
         <v>20</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K139" s="3"/>
       <c r="L139" s="4" t="s">
@@ -6180,10 +6201,10 @@
     </row>
     <row r="140">
       <c r="A140" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>15</v>
@@ -6192,10 +6213,10 @@
         <v>16</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G140" s="4">
         <v>480</v>
@@ -6207,7 +6228,7 @@
         <v>20</v>
       </c>
       <c r="J140" s="3" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="K140" s="3"/>
       <c r="L140" s="4" t="s">
@@ -6216,10 +6237,10 @@
     </row>
     <row r="141">
       <c r="A141" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>15</v>
@@ -6228,10 +6249,10 @@
         <v>16</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G141" s="4">
         <v>480</v>
@@ -6243,7 +6264,7 @@
         <v>20</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="K141" s="3"/>
       <c r="L141" s="4" t="s">
@@ -6252,10 +6273,10 @@
     </row>
     <row r="142">
       <c r="A142" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>15</v>
@@ -6264,13 +6285,13 @@
         <v>16</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="G142" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H142" s="3" t="s">
         <v>19</v>
@@ -6279,19 +6300,19 @@
         <v>20</v>
       </c>
       <c r="J142" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K142" s="3"/>
       <c r="L142" s="4" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>15</v>
@@ -6300,13 +6321,13 @@
         <v>16</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c r="G143" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H143" s="3" t="s">
         <v>19</v>
@@ -6315,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="J143" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K143" s="3"/>
       <c r="L143" s="4" t="s">
@@ -6324,10 +6345,10 @@
     </row>
     <row r="144">
       <c r="A144" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>15</v>
@@ -6336,13 +6357,13 @@
         <v>16</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>17</v>
+        <v>219</v>
       </c>
       <c r="G144" s="4">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>19</v>
@@ -6351,10 +6372,190 @@
         <v>20</v>
       </c>
       <c r="J144" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="K144" s="3"/>
       <c r="L144" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G145" s="4">
+        <v>480</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K145" s="3"/>
+      <c r="L145" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G146" s="4">
+        <v>480</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K146" s="3"/>
+      <c r="L146" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G147" s="4">
+        <v>90</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K147" s="3"/>
+      <c r="L147" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G148" s="4">
+        <v>480</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="K148" s="3"/>
+      <c r="L148" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G149" s="4">
+        <v>90</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K149" s="3"/>
+      <c r="L149" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,15 +58,42 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>03/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>03/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Tăng ca bảo trì</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
     <t>02645278</t>
   </si>
   <si>
     <t>Moha Mad Nazid</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
     <t>TU Extrusion</t>
   </si>
   <si>
@@ -76,37 +103,10 @@
     <t>05/10/2026 15:30:00</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>tăng ca hổ trợ nghiền</t>
   </si>
   <si>
     <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>03/10/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>03/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>Tăng ca bảo trì</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
   </si>
 </sst>
 </file>
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
@@ -625,7 +625,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>19</v>

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>tăng ca hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
   </si>
 </sst>
 </file>
@@ -638,7 +635,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,52 +58,298 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01921560</t>
+  </si>
+  <si>
+    <t>Trần Quang Hiệu</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất. </t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (Ca1)</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>10/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
     <t>02317843</t>
   </si>
   <si>
     <t>Đinh Hoàng Phúc</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
     <t>T Extrusion</t>
   </si>
   <si>
+    <t>Tăng ca setup line đùn PL21</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca3</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
     <t>03/10/2026 07:45:00</t>
   </si>
   <si>
     <t>03/10/2026 16:30:00</t>
   </si>
   <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t>Tăng ca bảo trì</t>
   </si>
   <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền</t>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca2 </t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>Lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT (ca1)</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 3)</t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
+  </si>
+  <si>
+    <t>02645250</t>
+  </si>
+  <si>
+    <t>Trần Xuân Bắc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT Trục </t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>hỗ trợ sản xuất</t>
   </si>
 </sst>
 </file>
@@ -613,25 +859,25 @@
         <v>15</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="8">
+        <v>480</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="8">
-        <v>90</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -639,354 +885,976 @@
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="8">
+        <v>480</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="K5" s="7"/>
-      <c r="L5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" s="2" customFormat="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="8">
+        <v>480</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="K6" s="7"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" s="2" customFormat="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="8">
+        <v>480</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="K7" s="7"/>
-      <c r="L7" s="8"/>
+      <c r="L7" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="8">
+        <v>480</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="K8" s="7"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" s="2" customFormat="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="8">
+        <v>480</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="A10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="8">
+        <v>480</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>46</v>
+      </c>
       <c r="K10" s="7"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="8">
+        <v>480</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="K11" s="7"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="A12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="8">
+        <v>480</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="K12" s="7"/>
-      <c r="L12" s="8"/>
+      <c r="L12" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="8">
+        <v>480</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="K13" s="7"/>
-      <c r="L13" s="8"/>
+      <c r="L13" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="8">
+        <v>90</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="K14" s="7"/>
-      <c r="L14" s="8"/>
+      <c r="L14" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="8">
+        <v>480</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="K15" s="7"/>
-      <c r="L15" s="8"/>
+      <c r="L15" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="8">
+        <v>90</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="K16" s="7"/>
-      <c r="L16" s="8"/>
+      <c r="L16" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="8">
+        <v>480</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="K17" s="7"/>
-      <c r="L17" s="8"/>
+      <c r="L17" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="8">
+        <v>480</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>75</v>
+      </c>
       <c r="K18" s="7"/>
-      <c r="L18" s="8"/>
+      <c r="L18" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="8">
+        <v>480</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="K19" s="7"/>
-      <c r="L19" s="8"/>
+      <c r="L19" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="A20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="8">
+        <v>480</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>81</v>
+      </c>
       <c r="K20" s="7"/>
-      <c r="L20" s="8"/>
+      <c r="L20" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="8">
+        <v>480</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="K21" s="7"/>
-      <c r="L21" s="8"/>
+      <c r="L21" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="A22" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="8">
+        <v>480</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="K22" s="7"/>
-      <c r="L22" s="8"/>
+      <c r="L22" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
+      <c r="A23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="8">
+        <v>480</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>88</v>
+      </c>
       <c r="K23" s="7"/>
-      <c r="L23" s="8"/>
+      <c r="L23" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="8">
+        <v>480</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="K24" s="7"/>
-      <c r="L24" s="8"/>
+      <c r="L24" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
+      <c r="A25" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="8">
+        <v>90</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="K25" s="7"/>
-      <c r="L25" s="8"/>
+      <c r="L25" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
+      <c r="A26" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="8">
+        <v>480</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="K26" s="7"/>
-      <c r="L26" s="8"/>
+      <c r="L26" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="8">
+        <v>480</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="K27" s="7"/>
-      <c r="L27" s="8"/>
+      <c r="L27" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="8">
+        <v>480</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>101</v>
+      </c>
       <c r="K28" s="7"/>
-      <c r="L28" s="8"/>
+      <c r="L28" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="A29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="8">
+        <v>480</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>104</v>
+      </c>
       <c r="K29" s="7"/>
-      <c r="L29" s="8"/>
+      <c r="L29" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="4">
+        <v>480</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="4">
+        <v>480</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -58,298 +58,406 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>03/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>03/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Tăng ca bảo trì</t>
+  </si>
+  <si>
+    <t>Chấp Nhận</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>05/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>05/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>08/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>hỗ trợ nghiền</t>
+  </si>
+  <si>
+    <t>09/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>09/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>10/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>11/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca3</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>10/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 1 </t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 1</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT (ca1)</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>10/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>10/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
     <t>01921560</t>
   </si>
   <si>
     <t>Trần Quang Hiệu</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>10/10/2026 22:00:00</t>
-  </si>
-  <si>
-    <t>11/10/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tăng ca hỗ trợ sản xuất. </t>
   </si>
   <si>
+    <t>02645250</t>
+  </si>
+  <si>
+    <t>Trần Xuân Bắc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT Trục </t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất ( ca 3)</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>Lắp đặt rack hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>Lắp đặt thiết bị</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca2 </t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất </t>
+  </si>
+  <si>
+    <t>Tăng ca setup line đùn PL21</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (Ca1)</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất (ca 2)</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>Thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02224288</t>
+  </si>
+  <si>
+    <t>Võ Văn Dương</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất ca 3. </t>
+  </si>
+  <si>
+    <t>12/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>12/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>13/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 20:30:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 22:00:00</t>
+  </si>
+  <si>
     <t>Chờ cấp trên gián tiếp</t>
   </si>
   <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>10/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>10/10/2026 06:00:00</t>
-  </si>
-  <si>
-    <t>Tăng ca hỗ trợ sản xuất (Ca1)</t>
+    <t>14/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>02644075</t>
+  </si>
+  <si>
+    <t>Huỳnh Đại Nhân</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vận hành máy nghiền </t>
   </si>
   <si>
     <t>Chưa duyệt</t>
   </si>
   <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>tăng ca sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>10/10/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>10/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca hổ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>Tăng ca setup line đùn PL21</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca3</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>05/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>05/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>tăng ca hổ trợ nghiền</t>
-  </si>
-  <si>
-    <t>Chấp Nhận</t>
-  </si>
-  <si>
-    <t>03/10/2026 07:45:00</t>
-  </si>
-  <si>
-    <t>03/10/2026 16:30:00</t>
-  </si>
-  <si>
-    <t>Tăng ca bảo trì</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>09/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>09/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>hỗ trợ nghiền</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>Lắp đặt rack hỗ trợ sản xuất</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tăng ca hỗ trợ sản xuất </t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất, ca 3</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca 1 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất </t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tăng ca sản xuất ca2 </t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>Lắp đặt thiết bị</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>08/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>TĂNG CA SẢN XUẤT (ca1)</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ca 1</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất ( ca 3)</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>tăng ca hỗ trợ sản xuất (ca 3)</t>
-  </si>
-  <si>
-    <t>02645250</t>
-  </si>
-  <si>
-    <t>Trần Xuân Bắc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT Trục </t>
-  </si>
-  <si>
-    <t>02228947</t>
-  </si>
-  <si>
-    <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>hỗ trợ sản xuất</t>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:30:00</t>
+  </si>
+  <si>
+    <t>vận hành máy nghiền</t>
+  </si>
+  <si>
+    <t>02644066</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tình</t>
+  </si>
+  <si>
+    <t>tăng ca Vân hành máy nghiêń</t>
   </si>
 </sst>
 </file>
@@ -859,16 +967,16 @@
         <v>15</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G4" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>19</v>
@@ -877,7 +985,7 @@
         <v>20</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8" t="s">
@@ -886,25 +994,25 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>19</v>
@@ -913,43 +1021,43 @@
         <v>20</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="8">
+        <v>90</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="8">
-        <v>480</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8" t="s">
@@ -958,22 +1066,22 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G7" s="8">
         <v>480</v>
@@ -985,7 +1093,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
@@ -994,22 +1102,22 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G8" s="8">
         <v>480</v>
@@ -1021,7 +1129,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="8" t="s">
@@ -1030,22 +1138,22 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G9" s="8">
         <v>480</v>
@@ -1057,7 +1165,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
@@ -1066,22 +1174,22 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G10" s="8">
         <v>480</v>
@@ -1093,32 +1201,32 @@
         <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="G11" s="8">
         <v>480</v>
       </c>
@@ -1129,31 +1237,31 @@
         <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G12" s="8">
         <v>480</v>
@@ -1165,31 +1273,31 @@
         <v>20</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G13" s="8">
         <v>480</v>
@@ -1201,7 +1309,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
@@ -1210,25 +1318,25 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G14" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>19</v>
@@ -1237,70 +1345,70 @@
         <v>20</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="8" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="8">
+        <v>480</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15" s="8">
-        <v>480</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>19</v>
@@ -1309,7 +1417,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="8" t="s">
@@ -1318,22 +1426,22 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G17" s="8">
         <v>480</v>
@@ -1345,11 +1453,11 @@
         <v>20</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
@@ -1363,13 +1471,13 @@
         <v>15</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G18" s="8">
         <v>480</v>
@@ -1399,13 +1507,13 @@
         <v>15</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G19" s="8">
         <v>480</v>
@@ -1421,7 +1529,7 @@
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
@@ -1435,13 +1543,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G20" s="8">
         <v>480</v>
@@ -1462,22 +1570,22 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G21" s="8">
         <v>480</v>
@@ -1489,31 +1597,31 @@
         <v>20</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G22" s="8">
         <v>480</v>
@@ -1525,31 +1633,31 @@
         <v>20</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="G23" s="8">
         <v>480</v>
@@ -1561,31 +1669,31 @@
         <v>20</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G24" s="8">
         <v>480</v>
@@ -1597,7 +1705,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
@@ -1606,25 +1714,25 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="G25" s="8">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
@@ -1633,31 +1741,31 @@
         <v>20</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G26" s="8">
         <v>480</v>
@@ -1669,7 +1777,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="8" t="s">
@@ -1687,13 +1795,13 @@
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G27" s="8">
         <v>480</v>
@@ -1723,13 +1831,13 @@
         <v>15</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G28" s="8">
         <v>480</v>
@@ -1745,15 +1853,15 @@
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>15</v>
@@ -1762,10 +1870,10 @@
         <v>16</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G29" s="8">
         <v>480</v>
@@ -1777,7 +1885,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
@@ -1786,34 +1894,34 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="4">
+        <v>480</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="4">
-        <v>480</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="4" t="s">
@@ -1822,38 +1930,542 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="4">
+        <v>480</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="4">
-        <v>480</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" s="4">
+        <v>480</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" s="4">
+        <v>480</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="4">
+        <v>480</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="4">
+        <v>480</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G36" s="4">
+        <v>480</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="4">
+        <v>90</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G38" s="4">
+        <v>90</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" s="4">
+        <v>90</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="4">
+        <v>90</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="4">
+        <v>90</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G42" s="4">
+        <v>90</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" s="4">
+        <v>90</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K43" s="3"/>
+      <c r="L43" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="4">
+        <v>90</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K44" s="3"/>
+      <c r="L44" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G45" s="4">
+        <v>90</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="K45" s="3"/>
+      <c r="L45" s="4" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/data/hrm_sync_plan_1.xlsx
+++ b/data/hrm_sync_plan_1.xlsx
@@ -412,52 +412,247 @@
     <t>14/10/2026 22:00:00</t>
   </si>
   <si>
+    <t>xe hư, không tăng ca</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>14/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>14/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>15/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>16/10/2026 15:30:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca2</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca hỗ trợ sản xuất </t>
+  </si>
+  <si>
+    <t>17/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>17/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>setup line PL01</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>18/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất. ca 3 </t>
+  </si>
+  <si>
+    <t>17/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca thứ 7 Short </t>
+  </si>
+  <si>
+    <t>Lắp rack hỗ trợ sản xuất.</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất Ca 3</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca 3</t>
+  </si>
+  <si>
+    <t>02660444</t>
+  </si>
+  <si>
+    <t>Võ Minh Đức</t>
+  </si>
+  <si>
+    <t>đóng thùng thành phẩm vận chuyển hàng ng</t>
+  </si>
+  <si>
+    <t>02661799</t>
+  </si>
+  <si>
+    <t>Đặng Lê Minh Tài</t>
+  </si>
+  <si>
+    <t>vận chuyển nguyên vật liệu</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 1)</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>Hủy tăng ca.</t>
+  </si>
+  <si>
+    <t>Tăng ca sản xuất</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng cường sản xuất </t>
+  </si>
+  <si>
+    <t>Tăng ca hỗ trợ sản xuất (Ca2)</t>
+  </si>
+  <si>
+    <t>02325295</t>
+  </si>
+  <si>
+    <t>Lưu Văn Đủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất  (ca2)</t>
+  </si>
+  <si>
+    <t>tăng ca hổ trợ nghiền ca 3</t>
+  </si>
+  <si>
+    <t>21/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>21/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Tăng ca triển khai bản vẽ cover máy nghiền.</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>22/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t>22/10/2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>Tăng ca hoàn thiện bản vẽ cover máy nghiền.</t>
+  </si>
+  <si>
+    <t>24/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>24/10/2026 14:00:00</t>
+  </si>
+  <si>
+    <t>tăng ca hỗ trợ sản xuất, ca 1</t>
+  </si>
+  <si>
     <t>Chờ cấp trên gián tiếp</t>
   </si>
   <si>
-    <t>14/10/2026 14:00:00</t>
-  </si>
-  <si>
-    <t>14/10/2026 15:30:00</t>
-  </si>
-  <si>
-    <t>02644075</t>
-  </si>
-  <si>
-    <t>Huỳnh Đại Nhân</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vận hành máy nghiền </t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02644057</t>
-  </si>
-  <si>
-    <t>Phạm Văn Công</t>
-  </si>
-  <si>
-    <t>14/10/2026 12:30:00</t>
-  </si>
-  <si>
-    <t>vận hành máy nghiền</t>
-  </si>
-  <si>
-    <t>02644066</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tình</t>
-  </si>
-  <si>
-    <t>tăng ca Vân hành máy nghiêń</t>
+    <t>tăng ca hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>24/10/2026 07:45:00</t>
+  </si>
+  <si>
+    <t>24/10/2026 16:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca hổ trợ sản xuất </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất  (ca1)</t>
+  </si>
+  <si>
+    <t>24/10/2026 22:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất.  ca 2 </t>
+  </si>
+  <si>
+    <t>25/10/2026 06:00:00</t>
+  </si>
+  <si>
+    <t>Hỗ trợ sản xuất(ca 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>Lắp rack hỗ trợ sản xuất</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất ca3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng ca sản xuất ca 2 </t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>TĂNG CA SẢN XUẤT (ca2)</t>
+  </si>
+  <si>
+    <t>thực hiện dự án cải tiến</t>
+  </si>
+  <si>
+    <t>tăng ca sản xuất Ca 2</t>
+  </si>
+  <si>
+    <t>tăng ca setup line PL01</t>
   </si>
 </sst>
 </file>
@@ -2319,9 +2514,11 @@
       <c r="J41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>131</v>
+      </c>
       <c r="L41" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42">
@@ -2338,10 +2535,10 @@
         <v>25</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G42" s="4">
         <v>90</v>
@@ -2357,115 +2554,1809 @@
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="4" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="G43" s="4">
         <v>90</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="4" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G44" s="4">
         <v>90</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="4" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G45" s="4">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>139</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" s="4">
+        <v>480</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K46" s="3"/>
+      <c r="L46" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G47" s="4">
+        <v>480</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="K47" s="3"/>
+      <c r="L47" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G48" s="4">
+        <v>480</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K48" s="3"/>
+      <c r="L48" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G49" s="4">
+        <v>480</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G50" s="4">
+        <v>480</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" s="4">
+        <v>480</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G52" s="4">
+        <v>480</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="4">
+        <v>480</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" s="4">
+        <v>480</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G55" s="4">
+        <v>480</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G56" s="4">
+        <v>480</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G57" s="4">
+        <v>480</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G58" s="4">
+        <v>480</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G59" s="4">
+        <v>480</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G60" s="4">
+        <v>480</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G61" s="4">
+        <v>480</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62" s="4">
+        <v>480</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G63" s="4">
+        <v>480</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K63" s="3"/>
+      <c r="L63" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G64" s="4">
+        <v>480</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="K64" s="3"/>
+      <c r="L64" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G65" s="4">
+        <v>480</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K65" s="3"/>
+      <c r="L65" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="4">
+        <v>480</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K66" s="3"/>
+      <c r="L66" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G67" s="4">
+        <v>480</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K67" s="3"/>
+      <c r="L67" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G68" s="4">
+        <v>480</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K68" s="3"/>
+      <c r="L68" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="G69" s="4">
+        <v>90</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K69" s="3"/>
+      <c r="L69" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G70" s="4">
+        <v>90</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K70" s="3"/>
+      <c r="L70" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G71" s="4">
+        <v>90</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K71" s="3"/>
+      <c r="L71" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G72" s="4">
+        <v>480</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="K72" s="3"/>
+      <c r="L72" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G73" s="4">
+        <v>480</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K73" s="3"/>
+      <c r="L73" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G74" s="4">
+        <v>480</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K74" s="3"/>
+      <c r="L74" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G75" s="4">
+        <v>480</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K75" s="3"/>
+      <c r="L75" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G76" s="4">
+        <v>480</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K76" s="3"/>
+      <c r="L76" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G77" s="4">
+        <v>480</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K77" s="3"/>
+      <c r="L77" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G78" s="4">
+        <v>480</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="K78" s="3"/>
+      <c r="L78" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G79" s="4">
+        <v>480</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K79" s="3"/>
+      <c r="L79" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G80" s="4">
+        <v>480</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K80" s="3"/>
+      <c r="L80" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G81" s="4">
+        <v>480</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="K81" s="3"/>
+      <c r="L81" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G82" s="4">
+        <v>480</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K82" s="3"/>
+      <c r="L82" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G83" s="4">
+        <v>480</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K83" s="3"/>
+      <c r="L83" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G84" s="4">
+        <v>480</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K84" s="3"/>
+      <c r="L84" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G85" s="4">
+        <v>480</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G86" s="4">
+        <v>480</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G87" s="4">
+        <v>480</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G88" s="4">
+        <v>480</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G89" s="4">
+        <v>480</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K89" s="3"/>
+      <c r="L89" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G90" s="4">
+        <v>480</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K90" s="3"/>
+      <c r="L90" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G91" s="4">
+        <v>480</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K91" s="3"/>
+      <c r="L91" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G92" s="4">
+        <v>480</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K92" s="3"/>
+      <c r="L92" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
